--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
         <v>12605000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>25210</v>
+        <v>25261</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -5909,14 +5909,14 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
         <v>12309000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>24618</v>
+        <v>24667</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -25052,7 +25052,7 @@
         </is>
       </c>
       <c r="E515" s="4" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
@@ -25061,14 +25061,14 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
         <v>10612000</v>
       </c>
       <c r="I515" s="5" t="n">
-        <v>23070</v>
+        <v>23020</v>
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
@@ -31982,10 +31982,10 @@
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>G | 500呎 (2房)
+          <t>G | 499呎 (2房)
 $1,260万
-$25,210/呎
-(26年-06月)</t>
+$25,261/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -32549,10 +32549,10 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>G | 500呎 (2房)
+          <t>G | 499呎 (2房)
 $1,231万
-$24,618/呎
-(26年-06月)</t>
+$24,667/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -34868,7 +34868,7 @@
           <t>J | 459呎 (2房)
 $998万
 $21,747/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -36213,7 +36213,7 @@
           <t>K | 329呎 (1房)
 $829万
 $25,185/呎
-(26年-05月)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -36352,10 +36352,10 @@
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>F | 460呎 (2房)
+          <t>F | 461呎 (2房)
 $1,061万
-$23,070/呎
-(26年-06月)</t>
+$23,020/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="H17" s="16" t="inlineStr">

--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2563,7 +2419,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -4451,7 +4307,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4543,7 +4399,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4873,7 +4729,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -5065,7 +4921,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6385,7 +6241,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6431,7 +6287,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-12</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -7705,7 +7561,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -14573,7 +14429,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14719,7 +14575,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14999,7 +14855,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -15191,7 +15047,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -15617,7 +15473,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15663,7 +15519,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -16519,7 +16375,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -17279,7 +17135,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -19041,7 +18897,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -19855,7 +19711,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -22503,7 +22359,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -22728,7 +22584,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -22737,14 +22593,14 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
         <v>10729000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>23324</v>
+        <v>23273</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -23393,7 +23249,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -23531,7 +23387,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -23660,7 +23516,7 @@
         </is>
       </c>
       <c r="E485" s="4" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
@@ -23669,14 +23525,14 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
         <v>10678000</v>
       </c>
       <c r="I485" s="5" t="n">
-        <v>23213</v>
+        <v>23163</v>
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
@@ -23857,7 +23713,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -23995,7 +23851,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -24459,7 +24315,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -24877,7 +24733,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -24923,7 +24779,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -25249,7 +25105,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -25387,7 +25243,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -25433,7 +25289,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -25571,7 +25427,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -25805,7 +25661,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -25851,7 +25707,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -25897,7 +25753,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -26315,7 +26171,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -26779,7 +26635,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -27105,7 +26961,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -27243,7 +27099,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -27569,7 +27425,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -27753,7 +27609,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -28171,7 +28027,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -28497,7 +28353,7 @@
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="H589" s="5" t="n">
@@ -28635,7 +28491,7 @@
       </c>
       <c r="G592" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="H592" s="5" t="n">
@@ -28681,7 +28537,7 @@
       </c>
       <c r="G593" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H593" s="5" t="n">
@@ -28961,7 +28817,7 @@
       </c>
       <c r="G599" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="H599" s="5" t="n">
@@ -29425,7 +29281,7 @@
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="H609" s="5" t="n">
@@ -29751,7 +29607,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H616" s="5" t="n">
@@ -31017,7 +30873,7 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
@@ -31365,6168 +31221,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Miami Quay I - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>173 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>120 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>53 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1335呎 (4+房)
-$4,168万
-$31,221/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 484呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 437呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,890万
-$26,391/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,724万
-$26,080/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,284万
-$26,480/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$733万
-$23,044/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,283万
-$25,660/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,884万
-$26,313/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,719万
-$26,002/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,280万
-$26,402/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$731万
-$22,975/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,280万
-$25,647/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,873万
-$26,155/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,708万
-$25,846/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,273万
-$26,245/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$726万
-$22,836/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,268万
-$25,417/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,867万
-$26,077/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,703万
-$25,769/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,269万
-$26,167/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$724万
-$22,770/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,264万
-$25,341/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,862万
-$25,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,698万
-$25,691/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,265万
-$26,087/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$722万
-$22,701/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,261万
-$25,265/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,856万
-$25,922/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,693万
-$25,616/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,261万
-$26,008/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$720万
-$22,635/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,264万
-$25,327/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,850万
-$25,842/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,688万
-$25,539/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,258万
-$25,932/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$718万
-$22,566/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,260万
-$25,261/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,845万
-$25,767/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,683万
-$25,461/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,254万
-$25,856/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$716万
-$22,500/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,257万
-$25,196/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,839万
-$25,689/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,678万
-$25,386/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,250万
-$25,777/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$713万
-$22,431/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,246万
-$24,966/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,834万
-$25,612/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,673万
-$25,310/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,246万
-$25,701/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$711万
-$22,365/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,242万
-$24,890/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,828万
-$25,535/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,668万
-$25,234/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 486呎 (2房)
-$1,243万
-$25,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$709万
-$22,299/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,238万
-$24,816/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,817万
-$25,383/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,658万
-$25,085/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,235万
-$25,470/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$705万
-$22,164/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,231万
-$24,667/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,812万
-$25,307/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,653万
-$25,008/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,232万
-$25,394/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$723万
-$22,726/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,227万
-$24,593/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,807万
-$25,232/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,648万
-$24,933/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,228万
-$25,318/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$701万
-$22,031/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,224万
-$24,521/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,801万
-$25,155/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,643万
-$24,859/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,224万
-$25,243/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$698万
-$21,965/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,234万
-$24,727/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,796万
-$25,081/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,692万
-$25,601/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,221万
-$25,167/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$696万
-$21,903/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,231万
-$24,667/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,790万
-$25,006/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,633万
-$24,711/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 486呎 (2房)
-$1,217万
-$25,039/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$694万
-$21,836/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,213万
-$24,301/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,785万
-$24,930/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,628万
-$24,637/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,213万
-$25,016/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$692万
-$21,770/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,209万
-$24,228/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,780万
-$24,858/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,624万
-$24,563/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,210万
-$24,942/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$690万
-$21,704/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 499呎 (2房)
-$1,205万
-$24,156/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,769万
-$24,708/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,614万
-$24,418/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,202万
-$24,794/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$686万
-$21,575/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,218万
-$24,358/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,764万
-$24,634/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,609万
-$24,343/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,199万
-$24,720/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$704万
-$22,123/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,215万
-$24,300/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,759万
-$24,561/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,604万
-$24,271/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,195万
-$24,645/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$682万
-$21,447/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,212万
-$24,242/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,753万
-$24,487/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,600万
-$24,198/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,192万
-$24,571/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 318呎 (1房)
-$680万
-$21,381/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,209万
-$24,182/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,748万
-$24,415/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 661呎 (3房)
-$1,595万
-$24,126/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 485呎 (2房)
-$1,188万
-$24,497/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 280呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 500呎 (2房)
-$1,206万
-$24,124/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Miami Quay I - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>225 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>95 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>C | 460呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,090万
-$23,840/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,087万
-$23,783/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,068万
-$23,076/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,085万
-$23,740/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,264万
-$25,947/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,260万
-$25,871/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,078万
-$23,580/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,256万
-$25,793/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,054万
-$22,760/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,069万
-$23,396/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$590万
-$23,580/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,051万
-$22,691/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,066万
-$23,324/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$588万
-$23,508/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,047万
-$22,622/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,063万
-$23,254/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$586万
-$23,440/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,044万
-$22,555/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,060万
-$23,186/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$584万
-$23,368/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,242万
-$25,503/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,041万
-$22,488/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,056万
-$23,116/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$582万
-$23,296/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,070万
-$23,305/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,237万
-$25,409/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,038万
-$22,421/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,053万
-$23,046/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$581万
-$23,232/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,066万
-$23,235/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,234万
-$25,333/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,035万
-$22,354/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,050万
-$22,978/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$579万
-$23,160/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,063万
-$23,166/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,226万
-$25,181/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,029万
-$22,222/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,044万
-$22,840/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$576万
-$23,024/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,201万
-$26,166/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,236万
-$25,382/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,026万
-$22,156/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,041万
-$22,772/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$574万
-$22,952/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$772万
-$23,895/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,054万
-$22,959/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,233万
-$25,322/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,023万
-$22,089/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,038万
-$22,705/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$588万
-$23,536/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$748万
-$23,167/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,080万
-$23,540/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,230万
-$25,261/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,020万
-$22,022/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,064万
-$23,280/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$587万
-$23,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$746万
-$23,096/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,048万
-$22,821/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,016万
-$21,955/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,172万
-$25,646/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$569万
-$22,748/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$845万
-$26,167/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,044万
-$22,752/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,208万
-$24,807/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,014万
-$21,890/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,058万
-$23,140/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$567万
-$22,680/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$742万
-$22,960/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,183万
-$25,778/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,204万
-$24,733/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,010万
-$21,825/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,025万
-$22,433/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$565万
-$22,612/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$739万
-$22,892/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,180万
-$25,699/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1,201万
-$24,661/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,008万
-$21,760/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,022万
-$22,368/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$564万
-$22,544/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$758万
-$23,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,158万
-$25,240/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,004万
-$21,685/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,016万
-$22,234/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$560万
-$22,412/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$733万
-$22,687/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$998万
-$21,747/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1,000万
-$21,598/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,013万
-$22,166/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$559万
-$22,344/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$731万
-$22,619/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,131万
-$24,638/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$997万
-$21,542/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1,010万
-$22,101/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$556万
-$22,232/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$721万
-$22,325/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,128万
-$24,564/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$981万
-$21,184/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$995万
-$21,775/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$563万
-$22,524/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$710万
-$21,997/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,124万
-$24,490/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$942万
-$20,339/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$961万
-$21,037/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$524万
-$20,968/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1,121万
-$24,418/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Miami Quay I - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>250 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>198 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>43 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,111万
-$25,079/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$769万
-$23,649/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,090万
-$23,644/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,079万
-$23,987/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$754万
-$23,946/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$812万
-$25,693/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,108万
-$25,002/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$766万
-$23,582/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,087万
-$23,588/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,077万
-$23,929/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$752万
-$23,876/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$810万
-$25,620/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,183万
-$25,336/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,104万
-$24,928/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$764万
-$23,511/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,085万
-$23,596/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,075万
-$23,887/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$750万
-$23,803/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$807万
-$25,541/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,176万
-$25,186/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,098万
-$24,779/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$760万
-$23,372/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,081万
-$23,493/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,070万
-$23,782/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$745万
-$23,660/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$802万
-$25,389/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,173万
-$25,109/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,094万
-$24,704/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$757万
-$23,302/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,078万
-$23,386/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,064万
-$23,649/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$743万
-$23,590/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$800万
-$25,313/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,590万
-$25,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,169万
-$25,034/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,091万
-$24,632/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$755万
-$23,231/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,076万
-$23,330/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,061万
-$23,578/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$741万
-$23,521/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$798万
-$25,237/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,751万
-$28,242/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,166万
-$24,959/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,088万
-$24,558/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$753万
-$23,160/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,073万
-$23,324/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,058万
-$23,507/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$739万
-$23,451/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$795万
-$25,161/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,536万
-$24,781/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,195万
-$25,593/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,085万
-$24,483/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$750万
-$23,092/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,070万
-$23,270/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,055万
-$23,436/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$736万
-$23,378/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$793万
-$25,089/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,532万
-$24,705/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-$1,192万
-$25,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,081万
-$24,411/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$748万
-$23,022/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,068万
-$23,213/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,052万
-$23,369/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$734万
-$23,308/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$813万
-$25,640/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$831万
-$25,261/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,527万
-$24,631/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-$1,188万
-$25,385/呎
-(22年-11月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,078万
-$24,336/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$746万
-$22,954/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,065万
-$23,157/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,048万
-$23,298/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$732万
-$23,238/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$810万
-$25,565/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$829万
-$25,185/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,730万
-$27,906/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,152万
-$24,664/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,075万
-$24,266/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$744万
-$22,883/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,063万
-$23,102/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,045万
-$23,227/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$730万
-$23,171/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$808万
-$25,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$836万
-$25,395/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,518万
-$24,484/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-$1,148万
-$24,538/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,072万
-$24,192/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$742万
-$22,815/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,061万
-$23,020/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,042万
-$23,158/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$728万
-$23,102/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$783万
-$24,710/呎
-(22年-09月)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$847万
-$25,745/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,715万
-$27,656/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,142万
-$24,443/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,065万
-$24,047/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$737万
-$22,680/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$1,056万
-$22,967/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,036万
-$23,020/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$744万
-$23,616/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$779万
-$24,565/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$819万
-$24,884/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,504万
-$24,266/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,138万
-$24,370/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,062万
-$23,975/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$735万
-$22,612/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,054万
-$22,863/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,033万
-$22,951/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$742万
-$23,546/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$798万
-$25,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$840万
-$25,517/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,704万
-$27,490/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,135万
-$24,296/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,059万
-$23,905/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$733万
-$22,545/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,052万
-$22,809/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,030万
-$22,882/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$719万
-$22,825/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$796万
-$25,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$814万
-$24,739/呎
-(22年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,496万
-$24,121/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,163万
-$24,912/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,056万
-$23,833/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$730万
-$22,477/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,036万
-$22,475/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,027万
-$22,816/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$717万
-$22,759/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$794万
-$25,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$811万
-$24,663/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,491万
-$24,048/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-$1,160万
-$24,784/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,053万
-$23,761/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$728万
-$22,409/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,033万
-$22,408/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,024万
-$22,747/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$715万
-$22,692/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$791万
-$24,959/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$809万
-$24,590/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,486万
-$23,976/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,124万
-$24,079/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,049万
-$23,688/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$726万
-$22,342/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,030万
-$22,341/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,020万
-$22,678/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$733万
-$23,263/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$767万
-$24,275/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$807万
-$24,517/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,482万
-$23,905/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,153万
-$24,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,046万
-$23,621/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$724万
-$22,277/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,027万
-$22,273/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,017万
-$22,609/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$710万
-$22,556/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$765万
-$24,203/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$804万
-$24,444/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,478万
-$23,834/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,150万
-$24,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,043万
-$23,549/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$722万
-$22,209/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,024万
-$22,208/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,014万
-$22,542/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$728万
-$23,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 317呎 (1房)
-$784万
-$24,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$802万
-$24,368/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,469万
-$23,692/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
-$1,111万
-$23,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,037万
-$23,409/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$718万
-$22,077/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,018万
-$22,076/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,008万
-$22,409/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$704万
-$22,352/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$758万
-$23,984/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$797万
-$24,225/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,664万
-$26,840/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,108万
-$23,722/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,034万
-$23,339/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$717万
-$22,068/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,015万
-$22,009/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,005万
-$22,342/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$704万
-$22,340/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$756万
-$23,915/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,659万
-$26,760/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,104万
-$23,649/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,031万
-$23,269/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$715万
-$21,994/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,012万
-$21,944/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1,002万
-$22,276/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$701万
-$22,267/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$753万
-$23,842/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,654万
-$26,681/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1,101万
-$23,580/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1,028万
-$23,199/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$707万
-$21,760/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1,002万
-$21,727/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$992万
-$22,053/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$691万
-$21,924/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$751万
-$23,769/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,649万
-$26,600/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 429呎 (2房)
-$1,108万
-$25,828/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 406呎 (2房)
-$999万
-$24,606/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$681万
-$20,963/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$972万
-$21,093/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$964万
-$21,411/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$681万
-$21,616/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$749万
-$23,699/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +155,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +236,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +672,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -31221,4 +31419,6168 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1335呎 (4+房)
+$4168万
+$31,221/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 484呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1890万
+$26,391/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1724万
+$26,080/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1284万
+$26,480/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$733万
+$23,044/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1283万
+$25,660/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1884万
+$26,313/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1719万
+$26,002/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1280万
+$26,402/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$731万
+$22,975/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1280万
+$25,647/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1873万
+$26,155/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1708万
+$25,846/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1273万
+$26,245/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$726万
+$22,836/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1268万
+$25,417/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1867万
+$26,077/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1703万
+$25,769/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1269万
+$26,167/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$724万
+$22,770/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1264万
+$25,341/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1862万
+$25,999/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1698万
+$25,691/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1265万
+$26,087/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$722万
+$22,701/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1261万
+$25,265/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1856万
+$25,922/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1693万
+$25,616/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1261万
+$26,008/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$720万
+$22,635/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1264万
+$25,327/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1850万
+$25,842/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1688万
+$25,539/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1258万
+$25,932/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$718万
+$22,566/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1260万
+$25,261/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1845万
+$25,767/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1683万
+$25,461/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1254万
+$25,856/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$716万
+$22,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1257万
+$25,196/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1839万
+$25,689/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1678万
+$25,386/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1250万
+$25,777/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$713万
+$22,431/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1246万
+$24,966/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1834万
+$25,612/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1673万
+$25,310/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1246万
+$25,701/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$711万
+$22,365/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1242万
+$24,890/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1828万
+$25,535/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1668万
+$25,234/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 486呎 (2房)
+$1243万
+$25,570/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$709万
+$22,299/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1238万
+$24,816/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1817万
+$25,383/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1658万
+$25,085/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1235万
+$25,470/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$705万
+$22,164/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1231万
+$24,667/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1812万
+$25,307/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1653万
+$25,008/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1232万
+$25,394/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$723万
+$22,726/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1227万
+$24,593/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1807万
+$25,232/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1648万
+$24,933/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1228万
+$25,318/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$701万
+$22,031/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1224万
+$24,521/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1801万
+$25,155/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1643万
+$24,859/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1224万
+$25,243/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$698万
+$21,965/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1234万
+$24,727/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1796万
+$25,081/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1692万
+$25,601/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1221万
+$25,167/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$696万
+$21,903/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1231万
+$24,667/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1790万
+$25,006/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1633万
+$24,711/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 486呎 (2房)
+$1217万
+$25,039/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$694万
+$21,836/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1213万
+$24,301/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1785万
+$24,930/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1628万
+$24,637/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1213万
+$25,016/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$692万
+$21,770/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1209万
+$24,228/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1780万
+$24,858/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1624万
+$24,563/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1210万
+$24,942/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$690万
+$21,704/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 499呎 (2房)
+$1205万
+$24,156/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1769万
+$24,708/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1614万
+$24,418/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1202万
+$24,794/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$686万
+$21,575/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1218万
+$24,358/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1764万
+$24,634/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1609万
+$24,343/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1199万
+$24,720/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$704万
+$22,123/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1215万
+$24,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1759万
+$24,561/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1604万
+$24,271/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1195万
+$24,645/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$682万
+$21,447/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1212万
+$24,242/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1753万
+$24,487/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1600万
+$24,198/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1192万
+$24,571/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 318呎 (1房)
+$680万
+$21,381/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1209万
+$24,182/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1748万
+$24,415/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 661呎 (3房)
+$1595万
+$24,126/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 485呎 (2房)
+$1188万
+$24,497/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 280呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 500呎 (2房)
+$1206万
+$24,124/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1090万
+$23,840/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1087万
+$23,783/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1068万
+$23,076/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1085万
+$23,740/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1264万
+$25,947/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1260万
+$25,871/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1078万
+$23,580/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1256万
+$25,793/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1054万
+$22,760/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1069万
+$23,396/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$590万
+$23,580/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1051万
+$22,691/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1066万
+$23,324/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$588万
+$23,508/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1047万
+$22,622/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1063万
+$23,254/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$586万
+$23,440/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1044万
+$22,555/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1060万
+$23,186/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$584万
+$23,368/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1242万
+$25,503/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1041万
+$22,488/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1056万
+$23,116/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$582万
+$23,296/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1070万
+$23,305/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1237万
+$25,409/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1038万
+$22,421/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1053万
+$23,046/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$581万
+$23,232/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1066万
+$23,235/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1234万
+$25,333/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1035万
+$22,354/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1050万
+$22,978/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$579万
+$23,160/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1063万
+$23,166/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1226万
+$25,181/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1029万
+$22,222/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1044万
+$22,840/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$576万
+$23,024/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1201万
+$26,166/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1236万
+$25,382/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1026万
+$22,156/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1041万
+$22,772/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$574万
+$22,952/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$772万
+$23,895/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1054万
+$22,959/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1233万
+$25,322/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1023万
+$22,089/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1038万
+$22,705/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$588万
+$23,536/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$748万
+$23,167/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1080万
+$23,540/呎
+(22年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1230万
+$25,261/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1020万
+$22,022/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1064万
+$23,280/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$587万
+$23,464/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$746万
+$23,096/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1048万
+$22,821/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1016万
+$21,955/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1172万
+$25,646/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$569万
+$22,748/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$845万
+$26,167/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1044万
+$22,752/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1208万
+$24,807/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1014万
+$21,890/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1058万
+$23,140/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$567万
+$22,680/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$742万
+$22,960/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1183万
+$25,778/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1204万
+$24,733/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1010万
+$21,825/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1025万
+$22,433/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$565万
+$22,612/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$739万
+$22,892/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1180万
+$25,699/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1201万
+$24,661/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1008万
+$21,760/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1022万
+$22,368/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$564万
+$22,544/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$758万
+$23,471/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1158万
+$25,240/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1004万
+$21,685/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1016万
+$22,234/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$560万
+$22,412/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$733万
+$22,687/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$998万
+$21,747/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1000万
+$21,598/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1013万
+$22,166/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$559万
+$22,344/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$731万
+$22,619/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1131万
+$24,638/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$997万
+$21,542/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1010万
+$22,101/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$556万
+$22,232/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$721万
+$22,325/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1128万
+$24,564/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$981万
+$21,184/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$995万
+$21,775/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$563万
+$22,524/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$710万
+$21,997/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1124万
+$24,490/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$942万
+$20,339/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$961万
+$21,037/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$524万
+$20,968/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1121万
+$24,418/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1111万
+$25,079/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$769万
+$23,649/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1090万
+$23,644/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1079万
+$23,987/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$754万
+$23,946/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$812万
+$25,693/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1108万
+$25,002/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$766万
+$23,582/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1087万
+$23,588/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1077万
+$23,929/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$752万
+$23,876/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$810万
+$25,620/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1183万
+$25,336/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1104万
+$24,928/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$764万
+$23,511/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$1085万
+$23,596/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1075万
+$23,887/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$750万
+$23,803/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$807万
+$25,541/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1176万
+$25,186/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1098万
+$24,779/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$760万
+$23,372/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$1081万
+$23,493/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1070万
+$23,782/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$745万
+$23,660/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$802万
+$25,389/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1173万
+$25,109/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1094万
+$24,704/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$757万
+$23,302/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1078万
+$23,386/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1064万
+$23,649/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$743万
+$23,590/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$800万
+$25,313/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1590万
+$25,637/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1169万
+$25,034/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1091万
+$24,632/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$755万
+$23,231/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1076万
+$23,330/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1061万
+$23,578/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$741万
+$23,521/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$798万
+$25,237/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1751万
+$28,242/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1166万
+$24,959/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1088万
+$24,558/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$753万
+$23,160/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1073万
+$23,273/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1058万
+$23,507/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$739万
+$23,451/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$795万
+$25,161/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1536万
+$24,781/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1195万
+$25,593/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1085万
+$24,483/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$750万
+$23,092/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$1070万
+$23,270/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1055万
+$23,436/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$736万
+$23,378/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$793万
+$25,089/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1532万
+$24,705/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+$1192万
+$25,462/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1081万
+$24,411/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$748万
+$23,022/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1068万
+$23,163/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1052万
+$23,369/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$734万
+$23,308/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$813万
+$25,640/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$831万
+$25,261/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1527万
+$24,631/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+$1188万
+$25,385/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1078万
+$24,336/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$746万
+$22,954/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$1065万
+$23,157/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1048万
+$23,298/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$732万
+$23,238/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$810万
+$25,565/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$829万
+$25,185/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1730万
+$27,906/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1152万
+$24,664/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1075万
+$24,266/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$744万
+$22,883/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$1063万
+$23,102/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1045万
+$23,227/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$730万
+$23,171/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$808万
+$25,486/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$836万
+$25,395/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1518万
+$24,484/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+$1148万
+$24,538/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1072万
+$24,192/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$742万
+$22,815/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1061万
+$23,020/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1042万
+$23,158/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$728万
+$23,102/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$783万
+$24,710/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$847万
+$25,745/呎
+(22年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1715万
+$27,656/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1142万
+$24,443/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1065万
+$24,047/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$737万
+$22,680/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$1056万
+$22,967/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1036万
+$23,020/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$744万
+$23,616/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$779万
+$24,565/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$819万
+$24,884/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1504万
+$24,266/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1138万
+$24,370/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1062万
+$23,975/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$735万
+$22,612/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1054万
+$22,863/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1033万
+$22,951/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$742万
+$23,546/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$798万
+$25,266/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$840万
+$25,517/呎
+(22年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1704万
+$27,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1135万
+$24,296/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1059万
+$23,905/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$733万
+$22,545/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1052万
+$22,809/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1030万
+$22,882/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$719万
+$22,825/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$796万
+$25,190/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$814万
+$24,739/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1496万
+$24,121/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1163万
+$24,912/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1056万
+$23,833/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$730万
+$22,477/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1036万
+$22,475/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1027万
+$22,816/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$717万
+$22,759/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$794万
+$25,114/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$811万
+$24,663/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1491万
+$24,048/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+$1160万
+$24,784/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1053万
+$23,761/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$728万
+$22,409/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1033万
+$22,408/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1024万
+$22,747/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$715万
+$22,692/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$791万
+$24,959/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$809万
+$24,590/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1486万
+$23,976/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1124万
+$24,079/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1049万
+$23,688/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$726万
+$22,342/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1030万
+$22,341/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1020万
+$22,678/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$733万
+$23,263/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$767万
+$24,275/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$807万
+$24,517/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1482万
+$23,905/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1153万
+$24,690/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1046万
+$23,621/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$724万
+$22,277/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1027万
+$22,273/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1017万
+$22,609/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$710万
+$22,556/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$765万
+$24,203/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$804万
+$24,444/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1478万
+$23,834/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1150万
+$24,617/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1043万
+$23,549/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$722万
+$22,209/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1024万
+$22,208/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1014万
+$22,542/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$728万
+$23,127/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 317呎 (1房)
+$784万
+$24,735/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$802万
+$24,368/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1469万
+$23,692/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+$1111万
+$23,741/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1037万
+$23,409/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$718万
+$22,077/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1018万
+$22,076/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1008万
+$22,409/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$704万
+$22,352/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$758万
+$23,984/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$797万
+$24,225/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1664万
+$26,840/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1108万
+$23,722/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1034万
+$23,339/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$717万
+$22,068/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1015万
+$22,009/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1005万
+$22,342/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$704万
+$22,340/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$756万
+$23,915/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1659万
+$26,760/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1104万
+$23,649/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1031万
+$23,269/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$715万
+$21,994/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1012万
+$21,944/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1002万
+$22,276/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$701万
+$22,267/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$753万
+$23,842/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1654万
+$26,681/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1101万
+$23,580/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1028万
+$23,199/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$707万
+$21,760/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1002万
+$21,727/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$992万
+$22,053/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$691万
+$21,924/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$751万
+$23,769/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1649万
+$26,600/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 429呎 (2房)
+$1108万
+$25,828/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 406呎 (2房)
+$999万
+$24,606/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$681万
+$20,963/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$972万
+$21,093/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$964万
+$21,411/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$681万
+$21,616/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$749万
+$23,699/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -672,7 +672,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
         <v>12830000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>25660</v>
+        <v>25711</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -21379,14 +21379,14 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
         <v>10807000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>23493</v>
+        <v>23443</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -24651,14 +24651,14 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
         <v>10627000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>23102</v>
+        <v>23052</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="G626" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H626" s="5" t="n">
@@ -31658,10 +31658,10 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>G | 500呎 (2房)
+          <t>G | 499呎 (2房)
 $1283万
-$25,660/呎
-(26年-06月)</t>
+$25,711/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -35710,10 +35710,10 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 460呎 (2房)
+          <t>F | 461呎 (2房)
 $1081万
-$23,493/呎
-(26年-06月)</t>
+$23,443/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -36319,10 +36319,10 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 460呎 (2房)
+          <t>F | 461呎 (2房)
 $1063万
-$23,102/呎
-(26年-06月)</t>
+$23,052/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -37358,7 +37358,7 @@
           <t>E | 325呎 (1房)
 $715万
 $21,994/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">

--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -10133,7 +10133,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -44173,7 +44173,7 @@
           <t>G | 499呎 (2房)
 $1215万
 $24,349/呎
-(26年-06月-20日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -44236,7 +44236,7 @@
           <t>G | 499呎 (2房)
 $1212万
 $24,291/呎
-(26年-06月-20日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -42808,7 +42808,7 @@
           <t>A | 1335呎 (4+房)
 $4168万
 $31,221/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -42857,7 +42857,7 @@
           <t>A | 716呎 (3房)
 $1890万
 $26,391/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -42865,7 +42865,7 @@
           <t>B | 661呎 (3房)
 $1724万
 $26,080/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -42873,7 +42873,7 @@
           <t>C | 485呎 (2房)
 $1284万
 $26,480/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -42881,7 +42881,7 @@
           <t>D | 318呎 (1房)
 $733万
 $23,044/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -42905,7 +42905,7 @@
           <t>G | 499呎 (2房)
 $1283万
 $25,711/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -42920,7 +42920,7 @@
           <t>A | 716呎 (3房)
 $1884万
 $26,313/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -42928,7 +42928,7 @@
           <t>B | 661呎 (3房)
 $1719万
 $26,002/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -42936,7 +42936,7 @@
           <t>C | 485呎 (2房)
 $1280万
 $26,402/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -42944,7 +42944,7 @@
           <t>D | 318呎 (1房)
 $731万
 $22,975/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -42968,7 +42968,7 @@
           <t>G | 499呎 (2房)
 $1280万
 $25,647/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -42983,7 +42983,7 @@
           <t>A | 716呎 (3房)
 $1873万
 $26,155/呎
-(24年-07月)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -42991,7 +42991,7 @@
           <t>B | 661呎 (3房)
 $1708万
 $25,846/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -42999,7 +42999,7 @@
           <t>C | 485呎 (2房)
 $1273万
 $26,245/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -43007,7 +43007,7 @@
           <t>D | 318呎 (1房)
 $726万
 $22,836/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -43031,7 +43031,7 @@
           <t>G | 499呎 (2房)
 $1268万
 $25,417/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -43046,7 +43046,7 @@
           <t>A | 716呎 (3房)
 $1867万
 $26,077/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -43054,7 +43054,7 @@
           <t>B | 661呎 (3房)
 $1703万
 $25,769/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -43062,7 +43062,7 @@
           <t>C | 485呎 (2房)
 $1269万
 $26,167/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -43070,7 +43070,7 @@
           <t>D | 318呎 (1房)
 $724万
 $22,770/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -43094,7 +43094,7 @@
           <t>G | 499呎 (2房)
 $1264万
 $25,341/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -43109,7 +43109,7 @@
           <t>A | 716呎 (3房)
 $1862万
 $25,999/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -43117,7 +43117,7 @@
           <t>B | 661呎 (3房)
 $1698万
 $25,691/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -43125,7 +43125,7 @@
           <t>C | 485呎 (2房)
 $1265万
 $26,087/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -43133,7 +43133,7 @@
           <t>D | 318呎 (1房)
 $722万
 $22,701/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -43157,7 +43157,7 @@
           <t>G | 499呎 (2房)
 $1261万
 $25,265/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -43172,7 +43172,7 @@
           <t>A | 716呎 (3房)
 $1856万
 $25,922/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -43180,7 +43180,7 @@
           <t>B | 661呎 (3房)
 $1693万
 $25,616/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -43188,7 +43188,7 @@
           <t>C | 485呎 (2房)
 $1261万
 $26,008/呎
-(25年-01月)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -43196,7 +43196,7 @@
           <t>D | 318呎 (1房)
 $720万
 $22,635/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -43220,7 +43220,7 @@
           <t>G | 499呎 (2房)
 $1264万
 $25,327/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -43235,7 +43235,7 @@
           <t>A | 716呎 (3房)
 $1850万
 $25,842/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -43243,7 +43243,7 @@
           <t>B | 661呎 (3房)
 $1688万
 $25,539/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -43251,7 +43251,7 @@
           <t>C | 485呎 (2房)
 $1258万
 $25,932/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -43259,7 +43259,7 @@
           <t>D | 318呎 (1房)
 $718万
 $22,566/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -43283,7 +43283,7 @@
           <t>G | 499呎 (2房)
 $1260万
 $25,261/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -43298,7 +43298,7 @@
           <t>A | 716呎 (3房)
 $1845万
 $25,767/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -43306,7 +43306,7 @@
           <t>B | 661呎 (3房)
 $1683万
 $25,461/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -43314,7 +43314,7 @@
           <t>C | 485呎 (2房)
 $1254万
 $25,856/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -43322,7 +43322,7 @@
           <t>D | 318呎 (1房)
 $716万
 $22,500/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -43346,7 +43346,7 @@
           <t>G | 499呎 (2房)
 $1257万
 $25,196/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -43361,7 +43361,7 @@
           <t>A | 716呎 (3房)
 $1839万
 $25,689/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -43369,7 +43369,7 @@
           <t>B | 661呎 (3房)
 $1678万
 $25,386/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -43377,7 +43377,7 @@
           <t>C | 485呎 (2房)
 $1250万
 $25,777/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -43385,7 +43385,7 @@
           <t>D | 318呎 (1房)
 $713万
 $22,431/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -43401,7 +43401,7 @@
           <t>F | 448呎 (2房)
 $1048万
 $23,400/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -43409,7 +43409,7 @@
           <t>G | 499呎 (2房)
 $1246万
 $24,966/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -43424,7 +43424,7 @@
           <t>A | 716呎 (3房)
 $1834万
 $25,612/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -43432,7 +43432,7 @@
           <t>B | 661呎 (3房)
 $1673万
 $25,310/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -43440,7 +43440,7 @@
           <t>C | 485呎 (2房)
 $1246万
 $25,701/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -43448,7 +43448,7 @@
           <t>D | 318呎 (1房)
 $711万
 $22,365/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -43472,7 +43472,7 @@
           <t>G | 499呎 (2房)
 $1242万
 $24,890/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -43487,7 +43487,7 @@
           <t>A | 716呎 (3房)
 $1828万
 $25,535/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -43495,7 +43495,7 @@
           <t>B | 661呎 (3房)
 $1668万
 $25,234/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -43503,7 +43503,7 @@
           <t>C | 486呎 (2房)
 $1243万
 $25,570/呎
-(22年-10月)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -43511,7 +43511,7 @@
           <t>D | 318呎 (1房)
 $709万
 $22,299/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -43535,7 +43535,7 @@
           <t>G | 499呎 (2房)
 $1238万
 $24,816/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -43550,7 +43550,7 @@
           <t>A | 716呎 (3房)
 $1817万
 $25,383/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -43558,7 +43558,7 @@
           <t>B | 661呎 (3房)
 $1658万
 $25,085/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -43566,7 +43566,7 @@
           <t>C | 485呎 (2房)
 $1235万
 $25,470/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -43574,7 +43574,7 @@
           <t>D | 318呎 (1房)
 $705万
 $22,164/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -43598,7 +43598,7 @@
           <t>G | 499呎 (2房)
 $1231万
 $24,667/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -43613,7 +43613,7 @@
           <t>A | 716呎 (3房)
 $1812万
 $25,307/呎
-(24年-07月)</t>
+(24年-07月-23日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43621,7 +43621,7 @@
           <t>B | 661呎 (3房)
 $1653万
 $25,008/呎
-(25年-03月)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -43629,7 +43629,7 @@
           <t>C | 485呎 (2房)
 $1232万
 $25,394/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -43637,7 +43637,7 @@
           <t>D | 318呎 (1房)
 $723万
 $22,726/呎
-(22年-10月)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -43661,7 +43661,7 @@
           <t>G | 499呎 (2房)
 $1227万
 $24,593/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -43676,7 +43676,7 @@
           <t>A | 716呎 (3房)
 $1807万
 $25,232/呎
-(24年-07月)</t>
+(24年-07月-28日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43684,7 +43684,7 @@
           <t>B | 661呎 (3房)
 $1648万
 $24,933/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -43692,7 +43692,7 @@
           <t>C | 485呎 (2房)
 $1228万
 $25,318/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -43700,7 +43700,7 @@
           <t>D | 318呎 (1房)
 $701万
 $22,031/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -43724,7 +43724,7 @@
           <t>G | 499呎 (2房)
 $1224万
 $24,521/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -43739,7 +43739,7 @@
           <t>A | 716呎 (3房)
 $1801万
 $25,155/呎
-(24年-07月)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -43747,7 +43747,7 @@
           <t>B | 661呎 (3房)
 $1643万
 $24,859/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -43755,7 +43755,7 @@
           <t>C | 485呎 (2房)
 $1224万
 $25,243/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -43763,7 +43763,7 @@
           <t>D | 318呎 (1房)
 $698万
 $21,965/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -43787,7 +43787,7 @@
           <t>G | 499呎 (2房)
 $1234万
 $24,727/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -43802,7 +43802,7 @@
           <t>A | 716呎 (3房)
 $1796万
 $25,081/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43810,7 +43810,7 @@
           <t>B | 661呎 (3房)
 $1692万
 $25,601/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -43818,7 +43818,7 @@
           <t>C | 485呎 (2房)
 $1221万
 $25,167/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -43826,7 +43826,7 @@
           <t>D | 318呎 (1房)
 $696万
 $21,903/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -43850,7 +43850,7 @@
           <t>G | 499呎 (2房)
 $1231万
 $24,667/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -43865,7 +43865,7 @@
           <t>A | 716呎 (3房)
 $1790万
 $25,006/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43873,7 +43873,7 @@
           <t>B | 661呎 (3房)
 $1633万
 $24,711/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -43881,7 +43881,7 @@
           <t>C | 486呎 (2房)
 $1217万
 $25,039/呎
-(23年-02月)</t>
+(23年-02月-12日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -43889,7 +43889,7 @@
           <t>D | 318呎 (1房)
 $694万
 $21,836/呎
-(22年-10月)</t>
+(22年-10月-02日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -43913,7 +43913,7 @@
           <t>G | 499呎 (2房)
 $1213万
 $24,301/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -43928,7 +43928,7 @@
           <t>A | 716呎 (3房)
 $1785万
 $24,930/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43936,7 +43936,7 @@
           <t>B | 661呎 (3房)
 $1628万
 $24,637/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -43944,7 +43944,7 @@
           <t>C | 485呎 (2房)
 $1213万
 $25,016/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -43952,7 +43952,7 @@
           <t>D | 318呎 (1房)
 $692万
 $21,770/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -43976,7 +43976,7 @@
           <t>G | 499呎 (2房)
 $1209万
 $24,228/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -43991,7 +43991,7 @@
           <t>A | 716呎 (3房)
 $1780万
 $24,858/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43999,7 +43999,7 @@
           <t>B | 661呎 (3房)
 $1624万
 $24,563/呎
-(24年-10月)</t>
+(24年-10月-13日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -44007,7 +44007,7 @@
           <t>C | 485呎 (2房)
 $1210万
 $24,942/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -44015,7 +44015,7 @@
           <t>D | 318呎 (1房)
 $690万
 $21,704/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -44039,7 +44039,7 @@
           <t>G | 499呎 (2房)
 $1205万
 $24,156/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -44054,7 +44054,7 @@
           <t>A | 716呎 (3房)
 $1769万
 $24,708/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -44062,7 +44062,7 @@
           <t>B | 661呎 (3房)
 $1614万
 $24,418/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -44070,7 +44070,7 @@
           <t>C | 485呎 (2房)
 $1202万
 $24,794/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -44078,7 +44078,7 @@
           <t>D | 318呎 (1房)
 $686万
 $21,575/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -44102,7 +44102,7 @@
           <t>G | 499呎 (2房)
 $1218万
 $24,407/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -44117,7 +44117,7 @@
           <t>A | 716呎 (3房)
 $1764万
 $24,634/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -44125,7 +44125,7 @@
           <t>B | 661呎 (3房)
 $1609万
 $24,343/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -44133,7 +44133,7 @@
           <t>C | 485呎 (2房)
 $1199万
 $24,720/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -44141,7 +44141,7 @@
           <t>D | 318呎 (1房)
 $704万
 $22,123/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -44165,7 +44165,7 @@
           <t>G | 499呎 (2房)
 $1215万
 $24,349/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -44180,7 +44180,7 @@
           <t>A | 716呎 (3房)
 $1759万
 $24,561/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -44188,7 +44188,7 @@
           <t>B | 661呎 (3房)
 $1604万
 $24,271/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -44196,7 +44196,7 @@
           <t>C | 485呎 (2房)
 $1195万
 $24,645/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -44204,7 +44204,7 @@
           <t>D | 318呎 (1房)
 $682万
 $21,447/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -44228,7 +44228,7 @@
           <t>G | 499呎 (2房)
 $1212万
 $24,291/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -44243,7 +44243,7 @@
           <t>A | 716呎 (3房)
 $1753万
 $24,487/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -44251,7 +44251,7 @@
           <t>B | 661呎 (3房)
 $1600万
 $24,198/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -44259,7 +44259,7 @@
           <t>C | 485呎 (2房)
 $1192万
 $24,571/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -44267,7 +44267,7 @@
           <t>D | 318呎 (1房)
 $680万
 $21,381/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -44291,7 +44291,7 @@
           <t>G | 499呎 (2房)
 $1209万
 $24,230/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -44306,7 +44306,7 @@
           <t>A | 716呎 (3房)
 $1748万
 $24,415/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -44314,7 +44314,7 @@
           <t>B | 661呎 (3房)
 $1595万
 $24,126/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -44322,7 +44322,7 @@
           <t>C | 485呎 (2房)
 $1188万
 $24,497/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -44354,7 +44354,7 @@
           <t>G | 500呎 (2房)
 $1206万
 $24,124/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -44546,7 +44546,7 @@
           <t>D | 457呎 (2房)
 $1090万
 $23,840/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -44625,7 +44625,7 @@
           <t>D | 457呎 (2房)
 $1087万
 $23,783/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -44696,7 +44696,7 @@
           <t>C | 463呎 (2房)
 $1068万
 $23,076/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -44704,7 +44704,7 @@
           <t>D | 457呎 (2房)
 $1085万
 $23,740/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -44759,7 +44759,7 @@
           <t>A | 487呎 (2房)
 $1264万
 $25,947/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -44783,7 +44783,7 @@
           <t>D | 457呎 (2房)
 $1080万
 $23,637/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -44838,7 +44838,7 @@
           <t>A | 487呎 (2房)
 $1260万
 $25,871/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -44862,7 +44862,7 @@
           <t>D | 457呎 (2房)
 $1078万
 $23,580/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -44917,7 +44917,7 @@
           <t>A | 487呎 (2房)
 $1256万
 $25,793/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -44933,7 +44933,7 @@
           <t>C | 463呎 (2房)
 $1054万
 $22,760/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -44941,7 +44941,7 @@
           <t>D | 457呎 (2房)
 $1069万
 $23,396/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -44949,7 +44949,7 @@
           <t>E | 250呎 (开放式)
 $590万
 $23,580/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -45012,7 +45012,7 @@
           <t>C | 463呎 (2房)
 $1051万
 $22,691/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -45020,7 +45020,7 @@
           <t>D | 457呎 (2房)
 $1066万
 $23,324/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -45028,7 +45028,7 @@
           <t>E | 250呎 (开放式)
 $588万
 $23,508/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -45091,7 +45091,7 @@
           <t>C | 463呎 (2房)
 $1047万
 $22,622/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -45099,7 +45099,7 @@
           <t>D | 457呎 (2房)
 $1063万
 $23,254/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -45107,7 +45107,7 @@
           <t>E | 250呎 (开放式)
 $586万
 $23,440/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -45170,7 +45170,7 @@
           <t>C | 463呎 (2房)
 $1044万
 $22,555/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -45178,7 +45178,7 @@
           <t>D | 457呎 (2房)
 $1060万
 $23,186/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -45186,7 +45186,7 @@
           <t>E | 250呎 (开放式)
 $584万
 $23,368/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -45233,7 +45233,7 @@
           <t>A | 487呎 (2房)
 $1242万
 $25,503/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -45249,7 +45249,7 @@
           <t>C | 463呎 (2房)
 $1041万
 $22,488/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -45257,7 +45257,7 @@
           <t>D | 457呎 (2房)
 $1056万
 $23,116/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -45265,7 +45265,7 @@
           <t>E | 250呎 (开放式)
 $582万
 $23,296/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -45297,7 +45297,7 @@
           <t>J | 459呎 (2房)
 $1070万
 $23,305/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -45312,7 +45312,7 @@
           <t>A | 487呎 (2房)
 $1237万
 $25,409/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -45328,7 +45328,7 @@
           <t>C | 463呎 (2房)
 $1038万
 $22,421/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -45336,7 +45336,7 @@
           <t>D | 457呎 (2房)
 $1053万
 $23,046/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -45344,7 +45344,7 @@
           <t>E | 250呎 (开放式)
 $581万
 $23,232/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -45376,7 +45376,7 @@
           <t>J | 459呎 (2房)
 $1066万
 $23,235/呎
-(26年-06月)</t>
+(26年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -45391,7 +45391,7 @@
           <t>A | 487呎 (2房)
 $1234万
 $25,333/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -45407,7 +45407,7 @@
           <t>C | 463呎 (2房)
 $1035万
 $22,354/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -45415,7 +45415,7 @@
           <t>D | 457呎 (2房)
 $1050万
 $22,978/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -45423,7 +45423,7 @@
           <t>E | 250呎 (开放式)
 $579万
 $23,160/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -45455,7 +45455,7 @@
           <t>J | 459呎 (2房)
 $1063万
 $23,166/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -45470,7 +45470,7 @@
           <t>A | 487呎 (2房)
 $1226万
 $25,181/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -45486,7 +45486,7 @@
           <t>C | 463呎 (2房)
 $1029万
 $22,222/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -45494,7 +45494,7 @@
           <t>D | 457呎 (2房)
 $1044万
 $22,840/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -45502,7 +45502,7 @@
           <t>E | 250呎 (开放式)
 $576万
 $23,024/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -45549,7 +45549,7 @@
           <t>A | 487呎 (2房)
 $1236万
 $25,382/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -45565,7 +45565,7 @@
           <t>C | 463呎 (2房)
 $1026万
 $22,156/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -45573,7 +45573,7 @@
           <t>D | 457呎 (2房)
 $1041万
 $22,772/呎
-(24年-07月)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -45581,7 +45581,7 @@
           <t>E | 250呎 (开放式)
 $574万
 $22,952/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -45589,7 +45589,7 @@
           <t>F | 323呎 (1房)
 $772万
 $23,895/呎
-(22年-10月)</t>
+(22年-10月-02日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -45613,7 +45613,7 @@
           <t>J | 459呎 (2房)
 $1054万
 $22,959/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -45628,7 +45628,7 @@
           <t>A | 487呎 (2房)
 $1233万
 $25,322/呎
-(26年-06月)</t>
+(26年-06月-27日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -45644,7 +45644,7 @@
           <t>C | 463呎 (2房)
 $1023万
 $22,089/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -45652,7 +45652,7 @@
           <t>D | 457呎 (2房)
 $1038万
 $22,705/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -45660,7 +45660,7 @@
           <t>E | 250呎 (开放式)
 $588万
 $23,536/呎
-(22年-10月)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -45668,7 +45668,7 @@
           <t>F | 323呎 (1房)
 $748万
 $23,167/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -45692,7 +45692,7 @@
           <t>J | 459呎 (2房)
 $1080万
 $23,540/呎
-(22年-09月)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -45707,7 +45707,7 @@
           <t>A | 487呎 (2房)
 $1230万
 $25,261/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -45723,7 +45723,7 @@
           <t>C | 463呎 (2房)
 $1020万
 $22,022/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -45731,7 +45731,7 @@
           <t>D | 457呎 (2房)
 $1064万
 $23,280/呎
-(22年-10月)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -45739,7 +45739,7 @@
           <t>E | 250呎 (开放式)
 $587万
 $23,464/呎
-(22年-10月)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -45747,7 +45747,7 @@
           <t>F | 323呎 (1房)
 $746万
 $23,096/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -45771,7 +45771,7 @@
           <t>J | 459呎 (2房)
 $1048万
 $22,821/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -45802,7 +45802,7 @@
           <t>C | 463呎 (2房)
 $1016万
 $21,955/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -45818,7 +45818,7 @@
           <t>E | 250呎 (开放式)
 $569万
 $22,748/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
@@ -45850,7 +45850,7 @@
           <t>J | 459呎 (2房)
 $1044万
 $22,752/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -45865,7 +45865,7 @@
           <t>A | 487呎 (2房)
 $1208万
 $24,807/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -45881,7 +45881,7 @@
           <t>C | 463呎 (2房)
 $1014万
 $21,890/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -45889,7 +45889,7 @@
           <t>D | 457呎 (2房)
 $1058万
 $23,140/呎
-(22年-10月)</t>
+(22年-10月-02日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -45897,7 +45897,7 @@
           <t>E | 250呎 (开放式)
 $567万
 $22,680/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -45905,7 +45905,7 @@
           <t>F | 323呎 (1房)
 $742万
 $22,960/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -45944,7 +45944,7 @@
           <t>A | 487呎 (2房)
 $1204万
 $24,733/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -45960,7 +45960,7 @@
           <t>C | 463呎 (2房)
 $1010万
 $21,825/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -45968,7 +45968,7 @@
           <t>D | 457呎 (2房)
 $1025万
 $22,433/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -45976,7 +45976,7 @@
           <t>E | 250呎 (开放式)
 $565万
 $22,612/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -45984,7 +45984,7 @@
           <t>F | 323呎 (1房)
 $739万
 $22,892/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -46023,7 +46023,7 @@
           <t>A | 487呎 (2房)
 $1201万
 $24,661/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -46039,7 +46039,7 @@
           <t>C | 463呎 (2房)
 $1008万
 $21,760/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -46047,7 +46047,7 @@
           <t>D | 457呎 (2房)
 $1022万
 $22,368/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -46055,7 +46055,7 @@
           <t>E | 250呎 (开放式)
 $564万
 $22,544/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -46063,7 +46063,7 @@
           <t>F | 323呎 (1房)
 $758万
 $23,471/呎
-(22年-10月)</t>
+(22年-10月-02日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -46118,7 +46118,7 @@
           <t>C | 463呎 (2房)
 $1004万
 $21,685/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -46126,7 +46126,7 @@
           <t>D | 457呎 (2房)
 $1016万
 $22,234/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -46134,7 +46134,7 @@
           <t>E | 250呎 (开放式)
 $560万
 $22,412/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -46142,7 +46142,7 @@
           <t>F | 323呎 (1房)
 $733万
 $22,687/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -46166,7 +46166,7 @@
           <t>J | 459呎 (2房)
 $998万
 $21,747/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -46197,7 +46197,7 @@
           <t>C | 463呎 (2房)
 $1000万
 $21,598/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -46205,7 +46205,7 @@
           <t>D | 457呎 (2房)
 $1013万
 $22,166/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -46213,7 +46213,7 @@
           <t>E | 250呎 (开放式)
 $559万
 $22,344/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -46221,7 +46221,7 @@
           <t>F | 323呎 (1房)
 $731万
 $22,619/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -46276,7 +46276,7 @@
           <t>C | 463呎 (2房)
 $997万
 $21,542/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -46284,7 +46284,7 @@
           <t>D | 457呎 (2房)
 $1010万
 $22,101/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -46292,7 +46292,7 @@
           <t>E | 250呎 (开放式)
 $556万
 $22,232/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -46300,7 +46300,7 @@
           <t>F | 323呎 (1房)
 $721万
 $22,325/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -46355,7 +46355,7 @@
           <t>C | 463呎 (2房)
 $981万
 $21,184/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -46363,7 +46363,7 @@
           <t>D | 457呎 (2房)
 $995万
 $21,775/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -46371,7 +46371,7 @@
           <t>E | 250呎 (开放式)
 $563万
 $22,524/呎
-(22年-10月)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -46379,7 +46379,7 @@
           <t>F | 323呎 (1房)
 $710万
 $21,997/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -46434,7 +46434,7 @@
           <t>C | 463呎 (2房)
 $942万
 $20,339/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -46442,7 +46442,7 @@
           <t>D | 457呎 (2房)
 $961万
 $21,037/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -46450,7 +46450,7 @@
           <t>E | 250呎 (开放式)
 $524万
 $20,968/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -46672,7 +46672,7 @@
           <t>C | 443呎 (2房)
 $1111万
 $25,079/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -46688,7 +46688,7 @@
           <t>E | 325呎 (1房)
 $769万
 $23,649/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -46696,7 +46696,7 @@
           <t>F | 461呎 (2房)
 $1090万
 $23,644/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -46704,7 +46704,7 @@
           <t>G | 450呎 (2房)
 $1079万
 $23,987/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -46712,7 +46712,7 @@
           <t>H | 315呎 (1房)
 $754万
 $23,946/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -46720,7 +46720,7 @@
           <t>J | 316呎 (1房)
 $812万
 $25,693/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -46759,7 +46759,7 @@
           <t>C | 443呎 (2房)
 $1108万
 $25,002/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -46775,7 +46775,7 @@
           <t>E | 325呎 (1房)
 $766万
 $23,582/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -46783,7 +46783,7 @@
           <t>F | 461呎 (2房)
 $1087万
 $23,588/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -46791,7 +46791,7 @@
           <t>G | 450呎 (2房)
 $1077万
 $23,929/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -46799,7 +46799,7 @@
           <t>H | 315呎 (1房)
 $752万
 $23,876/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -46807,7 +46807,7 @@
           <t>J | 316呎 (1房)
 $810万
 $25,620/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -46838,7 +46838,7 @@
           <t>B | 467呎 (2房)
 $1183万
 $25,336/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -46846,7 +46846,7 @@
           <t>C | 443呎 (2房)
 $1104万
 $24,928/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -46862,7 +46862,7 @@
           <t>E | 325呎 (1房)
 $764万
 $23,511/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -46870,7 +46870,7 @@
           <t>F | 461呎 (2房)
 $1085万
 $23,544/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -46878,7 +46878,7 @@
           <t>G | 450呎 (2房)
 $1075万
 $23,887/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -46886,7 +46886,7 @@
           <t>H | 315呎 (1房)
 $750万
 $23,803/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -46894,7 +46894,7 @@
           <t>J | 316呎 (1房)
 $807万
 $25,541/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -46925,7 +46925,7 @@
           <t>B | 467呎 (2房)
 $1176万
 $25,186/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -46933,7 +46933,7 @@
           <t>C | 443呎 (2房)
 $1098万
 $24,779/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -46949,7 +46949,7 @@
           <t>E | 325呎 (1房)
 $760万
 $23,372/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -46957,7 +46957,7 @@
           <t>F | 461呎 (2房)
 $1081万
 $23,443/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -46965,7 +46965,7 @@
           <t>G | 450呎 (2房)
 $1070万
 $23,782/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -46973,7 +46973,7 @@
           <t>H | 315呎 (1房)
 $745万
 $23,660/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -46981,7 +46981,7 @@
           <t>J | 316呎 (1房)
 $802万
 $25,389/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -47012,7 +47012,7 @@
           <t>B | 467呎 (2房)
 $1173万
 $25,109/呎
-(24年-08月)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -47020,7 +47020,7 @@
           <t>C | 443呎 (2房)
 $1094万
 $24,704/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -47036,7 +47036,7 @@
           <t>E | 325呎 (1房)
 $757万
 $23,302/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -47044,7 +47044,7 @@
           <t>F | 461呎 (2房)
 $1078万
 $23,386/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -47052,7 +47052,7 @@
           <t>G | 450呎 (2房)
 $1064万
 $23,649/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -47060,7 +47060,7 @@
           <t>H | 315呎 (1房)
 $743万
 $23,590/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -47068,7 +47068,7 @@
           <t>J | 316呎 (1房)
 $800万
 $25,313/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -47091,7 +47091,7 @@
           <t>A | 620呎 (3房)
 $1590万
 $25,637/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -47099,7 +47099,7 @@
           <t>B | 467呎 (2房)
 $1169万
 $25,034/呎
-(25年-01月)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -47107,7 +47107,7 @@
           <t>C | 443呎 (2房)
 $1091万
 $24,632/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -47123,7 +47123,7 @@
           <t>E | 325呎 (1房)
 $755万
 $23,231/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -47131,7 +47131,7 @@
           <t>F | 461呎 (2房)
 $1076万
 $23,330/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -47139,7 +47139,7 @@
           <t>G | 450呎 (2房)
 $1061万
 $23,578/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -47147,7 +47147,7 @@
           <t>H | 315呎 (1房)
 $741万
 $23,521/呎
-(26年-04月)</t>
+(26年-04月-06日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -47155,7 +47155,7 @@
           <t>J | 316呎 (1房)
 $798万
 $25,237/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -47186,7 +47186,7 @@
           <t>B | 467呎 (2房)
 $1166万
 $24,959/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -47194,7 +47194,7 @@
           <t>C | 443呎 (2房)
 $1088万
 $24,558/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -47210,7 +47210,7 @@
           <t>E | 325呎 (1房)
 $753万
 $23,160/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -47218,7 +47218,7 @@
           <t>F | 461呎 (2房)
 $1073万
 $23,273/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -47226,7 +47226,7 @@
           <t>G | 450呎 (2房)
 $1058万
 $23,507/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -47234,7 +47234,7 @@
           <t>H | 315呎 (1房)
 $739万
 $23,451/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -47242,7 +47242,7 @@
           <t>J | 316呎 (1房)
 $795万
 $25,161/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -47265,7 +47265,7 @@
           <t>A | 620呎 (3房)
 $1536万
 $24,781/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -47273,7 +47273,7 @@
           <t>B | 467呎 (2房)
 $1195万
 $25,593/呎
-(22年-09月)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -47281,7 +47281,7 @@
           <t>C | 443呎 (2房)
 $1085万
 $24,483/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -47297,7 +47297,7 @@
           <t>E | 325呎 (1房)
 $750万
 $23,092/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -47305,7 +47305,7 @@
           <t>F | 461呎 (2房)
 $1070万
 $23,219/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -47313,7 +47313,7 @@
           <t>G | 450呎 (2房)
 $1055万
 $23,436/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -47321,7 +47321,7 @@
           <t>H | 315呎 (1房)
 $736万
 $23,378/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -47329,7 +47329,7 @@
           <t>J | 316呎 (1房)
 $793万
 $25,089/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -47352,7 +47352,7 @@
           <t>A | 620呎 (3房)
 $1532万
 $24,705/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -47360,7 +47360,7 @@
           <t>B | 468呎 (2房)
 $1192万
 $25,462/呎
-(22年-10月)</t>
+(22年-10月-05日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -47368,7 +47368,7 @@
           <t>C | 443呎 (2房)
 $1081万
 $24,411/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -47384,7 +47384,7 @@
           <t>E | 325呎 (1房)
 $748万
 $23,022/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -47392,7 +47392,7 @@
           <t>F | 461呎 (2房)
 $1068万
 $23,163/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -47400,7 +47400,7 @@
           <t>G | 450呎 (2房)
 $1052万
 $23,369/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -47408,7 +47408,7 @@
           <t>H | 315呎 (1房)
 $734万
 $23,308/呎
-(24年-07月)</t>
+(24年-07月-09日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -47416,7 +47416,7 @@
           <t>J | 317呎 (1房)
 $813万
 $25,640/呎
-(22年-09月)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -47424,7 +47424,7 @@
           <t>K | 329呎 (1房)
 $831万
 $25,261/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -47439,7 +47439,7 @@
           <t>A | 620呎 (3房)
 $1527万
 $24,631/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -47447,7 +47447,7 @@
           <t>B | 468呎 (2房)
 $1188万
 $25,385/呎
-(22年-11月)</t>
+(22年-11月-23日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -47455,7 +47455,7 @@
           <t>C | 443呎 (2房)
 $1078万
 $24,336/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -47471,7 +47471,7 @@
           <t>E | 325呎 (1房)
 $746万
 $22,954/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -47479,7 +47479,7 @@
           <t>F | 461呎 (2房)
 $1065万
 $23,106/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -47487,7 +47487,7 @@
           <t>G | 450呎 (2房)
 $1048万
 $23,298/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -47495,7 +47495,7 @@
           <t>H | 315呎 (1房)
 $732万
 $23,238/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -47503,7 +47503,7 @@
           <t>J | 317呎 (1房)
 $810万
 $25,565/呎
-(22年-09月)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -47511,7 +47511,7 @@
           <t>K | 329呎 (1房)
 $829万
 $25,185/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -47534,7 +47534,7 @@
           <t>B | 467呎 (2房)
 $1152万
 $24,664/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -47542,7 +47542,7 @@
           <t>C | 443呎 (2房)
 $1075万
 $24,266/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -47558,7 +47558,7 @@
           <t>E | 325呎 (1房)
 $744万
 $22,883/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -47566,7 +47566,7 @@
           <t>F | 461呎 (2房)
 $1063万
 $23,052/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -47574,7 +47574,7 @@
           <t>G | 450呎 (2房)
 $1045万
 $23,227/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -47582,7 +47582,7 @@
           <t>H | 315呎 (1房)
 $730万
 $23,171/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -47590,7 +47590,7 @@
           <t>J | 317呎 (1房)
 $808万
 $25,486/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -47598,7 +47598,7 @@
           <t>K | 329呎 (1房)
 $836万
 $25,395/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -47613,7 +47613,7 @@
           <t>A | 620呎 (3房)
 $1518万
 $24,484/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -47621,7 +47621,7 @@
           <t>B | 468呎 (2房)
 $1148万
 $24,538/呎
-(23年-04月)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -47629,7 +47629,7 @@
           <t>C | 443呎 (2房)
 $1072万
 $24,192/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -47645,7 +47645,7 @@
           <t>E | 325呎 (1房)
 $742万
 $22,815/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -47653,7 +47653,7 @@
           <t>F | 461呎 (2房)
 $1061万
 $23,020/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -47661,7 +47661,7 @@
           <t>G | 450呎 (2房)
 $1042万
 $23,158/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -47669,7 +47669,7 @@
           <t>H | 315呎 (1房)
 $728万
 $23,102/呎
-(24年-06月)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -47677,7 +47677,7 @@
           <t>J | 317呎 (1房)
 $783万
 $24,710/呎
-(22年-09月)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -47685,7 +47685,7 @@
           <t>K | 329呎 (1房)
 $847万
 $25,745/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -47708,7 +47708,7 @@
           <t>B | 467呎 (2房)
 $1142万
 $24,443/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -47716,7 +47716,7 @@
           <t>C | 443呎 (2房)
 $1065万
 $24,047/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -47732,7 +47732,7 @@
           <t>E | 325呎 (1房)
 $737万
 $22,680/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -47740,7 +47740,7 @@
           <t>F | 461呎 (2房)
 $1056万
 $22,918/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -47748,7 +47748,7 @@
           <t>G | 450呎 (2房)
 $1036万
 $23,020/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -47756,7 +47756,7 @@
           <t>H | 315呎 (1房)
 $744万
 $23,616/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -47764,7 +47764,7 @@
           <t>J | 317呎 (1房)
 $779万
 $24,565/呎
-(23年-03月)</t>
+(23年-03月-22日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -47772,7 +47772,7 @@
           <t>K | 329呎 (1房)
 $819万
 $24,884/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -47787,7 +47787,7 @@
           <t>A | 620呎 (3房)
 $1504万
 $24,266/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -47795,7 +47795,7 @@
           <t>B | 467呎 (2房)
 $1138万
 $24,370/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -47803,7 +47803,7 @@
           <t>C | 443呎 (2房)
 $1062万
 $23,975/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -47819,7 +47819,7 @@
           <t>E | 325呎 (1房)
 $735万
 $22,612/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -47827,7 +47827,7 @@
           <t>F | 461呎 (2房)
 $1054万
 $22,863/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -47835,7 +47835,7 @@
           <t>G | 450呎 (2房)
 $1033万
 $22,951/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -47843,7 +47843,7 @@
           <t>H | 315呎 (1房)
 $742万
 $23,546/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -47851,7 +47851,7 @@
           <t>J | 316呎 (1房)
 $798万
 $25,266/呎
-(22年-09月)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -47859,7 +47859,7 @@
           <t>K | 329呎 (1房)
 $840万
 $25,517/呎
-(22年-10月)</t>
+(22年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -47882,7 +47882,7 @@
           <t>B | 467呎 (2房)
 $1135万
 $24,296/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -47890,7 +47890,7 @@
           <t>C | 443呎 (2房)
 $1059万
 $23,905/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -47906,7 +47906,7 @@
           <t>E | 325呎 (1房)
 $733万
 $22,545/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -47914,7 +47914,7 @@
           <t>F | 461呎 (2房)
 $1052万
 $22,809/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -47922,7 +47922,7 @@
           <t>G | 450呎 (2房)
 $1030万
 $22,882/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -47930,7 +47930,7 @@
           <t>H | 315呎 (1房)
 $719万
 $22,825/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -47938,7 +47938,7 @@
           <t>J | 316呎 (1房)
 $796万
 $25,190/呎
-(22年-09月)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -47946,7 +47946,7 @@
           <t>K | 329呎 (1房)
 $814万
 $24,739/呎
-(22年-12月)</t>
+(22年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -47961,7 +47961,7 @@
           <t>A | 620呎 (3房)
 $1496万
 $24,121/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -47969,7 +47969,7 @@
           <t>B | 467呎 (2房)
 $1163万
 $24,912/呎
-(22年-09月)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -47977,7 +47977,7 @@
           <t>C | 443呎 (2房)
 $1056万
 $23,833/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -47993,7 +47993,7 @@
           <t>E | 325呎 (1房)
 $730万
 $22,477/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -48001,7 +48001,7 @@
           <t>F | 461呎 (2房)
 $1036万
 $22,475/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -48009,7 +48009,7 @@
           <t>G | 450呎 (2房)
 $1027万
 $22,816/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -48017,7 +48017,7 @@
           <t>H | 315呎 (1房)
 $717万
 $22,759/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -48025,7 +48025,7 @@
           <t>J | 316呎 (1房)
 $794万
 $25,114/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -48033,7 +48033,7 @@
           <t>K | 329呎 (1房)
 $811万
 $24,663/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -48048,7 +48048,7 @@
           <t>A | 620呎 (3房)
 $1491万
 $24,048/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -48056,7 +48056,7 @@
           <t>B | 468呎 (2房)
 $1160万
 $24,784/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -48064,7 +48064,7 @@
           <t>C | 443呎 (2房)
 $1053万
 $23,761/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -48080,7 +48080,7 @@
           <t>E | 325呎 (1房)
 $728万
 $22,409/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -48088,7 +48088,7 @@
           <t>F | 461呎 (2房)
 $1033万
 $22,408/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -48096,7 +48096,7 @@
           <t>G | 450呎 (2房)
 $1024万
 $22,747/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -48104,7 +48104,7 @@
           <t>H | 315呎 (1房)
 $715万
 $22,692/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -48112,7 +48112,7 @@
           <t>J | 317呎 (1房)
 $791万
 $24,959/呎
-(22年-09月)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -48120,7 +48120,7 @@
           <t>K | 329呎 (1房)
 $809万
 $24,590/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -48135,7 +48135,7 @@
           <t>A | 620呎 (3房)
 $1486万
 $23,976/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -48143,7 +48143,7 @@
           <t>B | 467呎 (2房)
 $1124万
 $24,079/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -48151,7 +48151,7 @@
           <t>C | 443呎 (2房)
 $1049万
 $23,688/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -48167,7 +48167,7 @@
           <t>E | 325呎 (1房)
 $726万
 $22,342/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -48175,7 +48175,7 @@
           <t>F | 461呎 (2房)
 $1030万
 $22,341/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -48183,7 +48183,7 @@
           <t>G | 450呎 (2房)
 $1020万
 $22,678/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -48191,7 +48191,7 @@
           <t>H | 315呎 (1房)
 $733万
 $23,263/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -48199,7 +48199,7 @@
           <t>J | 316呎 (1房)
 $767万
 $24,275/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -48207,7 +48207,7 @@
           <t>K | 329呎 (1房)
 $807万
 $24,517/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -48222,7 +48222,7 @@
           <t>A | 620呎 (3房)
 $1482万
 $23,905/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -48230,7 +48230,7 @@
           <t>B | 467呎 (2房)
 $1153万
 $24,690/呎
-(22年-10月)</t>
+(22年-10月-10日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -48238,7 +48238,7 @@
           <t>C | 443呎 (2房)
 $1046万
 $23,621/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -48254,7 +48254,7 @@
           <t>E | 325呎 (1房)
 $724万
 $22,277/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -48262,7 +48262,7 @@
           <t>F | 461呎 (2房)
 $1027万
 $22,273/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -48270,7 +48270,7 @@
           <t>G | 450呎 (2房)
 $1017万
 $22,609/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -48278,7 +48278,7 @@
           <t>H | 315呎 (1房)
 $710万
 $22,556/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -48286,7 +48286,7 @@
           <t>J | 316呎 (1房)
 $765万
 $24,203/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -48294,7 +48294,7 @@
           <t>K | 329呎 (1房)
 $804万
 $24,444/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -48309,7 +48309,7 @@
           <t>A | 620呎 (3房)
 $1478万
 $23,834/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -48317,7 +48317,7 @@
           <t>B | 467呎 (2房)
 $1150万
 $24,617/呎
-(22年-10月)</t>
+(22年-10月-04日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -48325,7 +48325,7 @@
           <t>C | 443呎 (2房)
 $1043万
 $23,549/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -48341,7 +48341,7 @@
           <t>E | 325呎 (1房)
 $722万
 $22,209/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -48349,7 +48349,7 @@
           <t>F | 461呎 (2房)
 $1024万
 $22,208/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -48357,7 +48357,7 @@
           <t>G | 450呎 (2房)
 $1014万
 $22,542/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -48365,7 +48365,7 @@
           <t>H | 315呎 (1房)
 $728万
 $23,127/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -48373,7 +48373,7 @@
           <t>J | 317呎 (1房)
 $784万
 $24,735/呎
-(22年-10月)</t>
+(22年-10月-09日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -48381,7 +48381,7 @@
           <t>K | 329呎 (1房)
 $802万
 $24,368/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -48396,7 +48396,7 @@
           <t>A | 620呎 (3房)
 $1469万
 $23,692/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -48404,7 +48404,7 @@
           <t>B | 468呎 (2房)
 $1111万
 $23,741/呎
-(22年-10月)</t>
+(22年-10月-06日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -48412,7 +48412,7 @@
           <t>C | 443呎 (2房)
 $1037万
 $23,409/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -48428,7 +48428,7 @@
           <t>E | 325呎 (1房)
 $718万
 $22,077/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -48436,7 +48436,7 @@
           <t>F | 461呎 (2房)
 $1018万
 $22,076/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -48444,7 +48444,7 @@
           <t>G | 450呎 (2房)
 $1008万
 $22,409/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -48452,7 +48452,7 @@
           <t>H | 315呎 (1房)
 $704万
 $22,352/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -48460,7 +48460,7 @@
           <t>J | 316呎 (1房)
 $758万
 $23,984/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -48468,7 +48468,7 @@
           <t>K | 329呎 (1房)
 $797万
 $24,225/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -48491,7 +48491,7 @@
           <t>B | 467呎 (2房)
 $1108万
 $23,722/呎
-(24年-07月)</t>
+(24年-07月-28日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -48499,7 +48499,7 @@
           <t>C | 443呎 (2房)
 $1034万
 $23,339/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -48515,7 +48515,7 @@
           <t>E | 325呎 (1房)
 $717万
 $22,068/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -48523,7 +48523,7 @@
           <t>F | 461呎 (2房)
 $1015万
 $22,009/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -48531,7 +48531,7 @@
           <t>G | 450呎 (2房)
 $1005万
 $22,342/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -48539,7 +48539,7 @@
           <t>H | 315呎 (1房)
 $704万
 $22,340/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -48547,7 +48547,7 @@
           <t>J | 316呎 (1房)
 $756万
 $23,915/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -48578,7 +48578,7 @@
           <t>B | 467呎 (2房)
 $1104万
 $23,649/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -48586,7 +48586,7 @@
           <t>C | 443呎 (2房)
 $1031万
 $23,269/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -48602,7 +48602,7 @@
           <t>E | 325呎 (1房)
 $715万
 $21,994/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -48610,7 +48610,7 @@
           <t>F | 461呎 (2房)
 $1012万
 $21,944/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -48618,7 +48618,7 @@
           <t>G | 450呎 (2房)
 $1002万
 $22,276/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -48626,7 +48626,7 @@
           <t>H | 315呎 (1房)
 $701万
 $22,267/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -48634,7 +48634,7 @@
           <t>J | 316呎 (1房)
 $753万
 $23,842/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -48665,7 +48665,7 @@
           <t>B | 467呎 (2房)
 $1101万
 $23,580/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -48673,7 +48673,7 @@
           <t>C | 443呎 (2房)
 $1028万
 $23,199/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -48689,7 +48689,7 @@
           <t>E | 325呎 (1房)
 $707万
 $21,760/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -48697,7 +48697,7 @@
           <t>F | 461呎 (2房)
 $1002万
 $21,727/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -48705,7 +48705,7 @@
           <t>G | 450呎 (2房)
 $992万
 $22,053/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -48713,7 +48713,7 @@
           <t>H | 315呎 (1房)
 $691万
 $21,924/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -48721,7 +48721,7 @@
           <t>J | 316呎 (1房)
 $751万
 $23,769/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -48752,7 +48752,7 @@
           <t>B | 429呎 (2房)
 $1108万
 $25,828/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -48760,7 +48760,7 @@
           <t>C | 406呎 (2房)
 $999万
 $24,606/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -48776,7 +48776,7 @@
           <t>E | 325呎 (1房)
 $681万
 $20,963/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -48784,7 +48784,7 @@
           <t>F | 461呎 (2房)
 $972万
 $21,093/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -48792,7 +48792,7 @@
           <t>G | 450呎 (2房)
 $964万
 $21,411/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -48800,7 +48800,7 @@
           <t>H | 315呎 (1房)
 $681万
 $21,616/呎
-(22年-09月)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -48808,7 +48808,7 @@
           <t>J | 316呎 (1房)
 $749万
 $23,699/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">

--- a/files/九龙-启德-Miami Quay I.xlsx
+++ b/files/九龙-启德-Miami Quay I.xlsx
@@ -11672,7 +11672,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -11680,34 +11680,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H172" s="5" t="n">
+        <v>7606000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>27164</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>6693280</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>23905</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -11998,7 +11990,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12006,34 +11998,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>7194000</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>28661</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>6330720</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>25222</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -12208,7 +12192,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12216,34 +12200,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>6820000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>27280</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>6001600</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>24006</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12620,7 +12596,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12628,34 +12604,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H186" s="5" t="n">
+        <v>7172000</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>28574</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>6311360</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>25145</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -12760,7 +12728,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -12768,34 +12736,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H188" s="5" t="n">
+        <v>8893000</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>27533</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>7825840</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>24229</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -12830,7 +12790,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -12838,34 +12798,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>6799000</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>27196</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>5983120</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>23932</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -13242,7 +13194,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -13250,34 +13202,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H195" s="5" t="n">
+        <v>7151000</v>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>28490</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>6292880</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>25071</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -13382,7 +13326,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13390,34 +13334,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H197" s="5" t="n">
+        <v>8867000</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>27452</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>7802960</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>24158</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr">
@@ -13452,7 +13388,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -13460,34 +13396,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H198" s="5" t="n">
+        <v>6779000</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>27116</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L198" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>5965520</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>23862</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13856,7 +13784,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -13864,34 +13792,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H204" s="5" t="n">
+        <v>7108000</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>28319</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>6255040</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>24920</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
@@ -13996,7 +13916,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14004,34 +13924,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H206" s="5" t="n">
+        <v>8814000</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>27288</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>7756320</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>24013</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -14066,7 +13978,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -14074,34 +13986,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H207" s="5" t="n">
+        <v>6739000</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>26956</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L207" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>5930320</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>23721</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14470,7 +14374,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14478,34 +14382,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>7087000</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>28235</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>6236560</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>24847</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -14610,7 +14506,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -14618,34 +14514,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>8788000</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>27207</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>7733440</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>23943</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -14680,7 +14568,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14688,34 +14576,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H216" s="5" t="n">
+        <v>6718000</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>26872</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>5911840</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>23647</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
@@ -15084,7 +14964,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15092,34 +14972,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>7065000</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>28147</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>6217200</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>24770</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -15224,7 +15096,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15232,34 +15104,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>8761000</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>27124</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>7709680</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>23869</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -15682,7 +15546,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -15690,34 +15554,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H231" s="5" t="n">
+        <v>7044000</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>28064</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L231" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>6198720</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>24696</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -15822,7 +15678,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15830,34 +15686,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>8735000</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>27043</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7686800</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>23798</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -16288,7 +16136,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16296,34 +16144,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H240" s="5" t="n">
+        <v>7023000</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>27980</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>6180240</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>24622</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -16428,7 +16268,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16436,34 +16276,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H242" s="5" t="n">
+        <v>8709000</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>26963</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L242" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>7663920</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>23727</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -16894,7 +16726,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -16902,34 +16734,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H249" s="5" t="n">
+        <v>7002000</v>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>27896</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>6161760</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>24549</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -17034,7 +16858,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -17042,34 +16866,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H251" s="5" t="n">
+        <v>8683000</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>26882</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L251" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>7641040</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>23656</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -17492,7 +17308,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -17500,34 +17316,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H258" s="5" t="n">
+        <v>6981000</v>
+      </c>
+      <c r="I258" s="5" t="n">
+        <v>27813</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L258" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>6143280</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>24475</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -17632,7 +17440,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17640,34 +17448,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H260" s="5" t="n">
+        <v>8657000</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>26802</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>7618160</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>23586</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -18082,7 +17882,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -18090,34 +17890,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H267" s="5" t="n">
+        <v>6960000</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>27729</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>6124800</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>24402</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -18222,7 +18014,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -18230,34 +18022,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H269" s="5" t="n">
+        <v>8631000</v>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>26721</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L269" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>7595280</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>23515</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -18672,7 +18456,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -18680,34 +18464,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H276" s="5" t="n">
+        <v>6940000</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>27649</v>
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L276" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>6107200</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>24331</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
@@ -18812,7 +18588,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -18820,34 +18596,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H278" s="5" t="n">
+        <v>8605000</v>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>26641</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L278" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>7572400</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>23444</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
@@ -19262,7 +19030,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -19270,34 +19038,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H285" s="5" t="n">
+        <v>6898000</v>
+      </c>
+      <c r="I285" s="5" t="n">
+        <v>27482</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L285" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>6070240</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>24184</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
@@ -19402,7 +19162,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -19410,34 +19170,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H287" s="5" t="n">
+        <v>8554000</v>
+      </c>
+      <c r="I287" s="5" t="n">
+        <v>26483</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L287" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>7527520</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>23305</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
@@ -19852,7 +19604,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -19860,34 +19612,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H294" s="5" t="n">
+        <v>6878000</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>27402</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>6052640</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>24114</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -20434,7 +20178,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -20442,34 +20186,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H303" s="5" t="n">
+        <v>6857000</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>27319</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="n">
+        <v>6034160</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>24040</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N303" s="3" t="inlineStr">
@@ -21016,7 +20752,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -21024,34 +20760,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H312" s="5" t="n">
+        <v>6837000</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>27239</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K312" s="5" t="n">
+        <v>6016560</v>
+      </c>
+      <c r="L312" s="5" t="n">
+        <v>23970</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -21598,7 +21326,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -21606,34 +21334,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H321" s="5" t="n">
+        <v>6816000</v>
+      </c>
+      <c r="I321" s="5" t="n">
+        <v>27155</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L321" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K321" s="5" t="n">
+        <v>5998080</v>
+      </c>
+      <c r="L321" s="5" t="n">
+        <v>23897</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N321" s="3" t="inlineStr">
@@ -22188,7 +21908,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -22196,34 +21916,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H330" s="5" t="n">
+        <v>6796000</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>27076</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K330" s="5" t="n">
+        <v>5980480</v>
+      </c>
+      <c r="L330" s="5" t="n">
+        <v>23827</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -22770,7 +22482,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -22778,34 +22490,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H339" s="5" t="n">
+        <v>6775000</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>26992</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>5962000</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>23753</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N339" s="3" t="inlineStr">
@@ -23352,7 +23056,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -23360,34 +23064,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H348" s="5" t="n">
+        <v>6654000</v>
+      </c>
+      <c r="I348" s="5" t="n">
+        <v>26510</v>
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L348" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K348" s="5" t="n">
+        <v>5855520</v>
+      </c>
+      <c r="L348" s="5" t="n">
+        <v>23329</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -23934,7 +23630,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -23942,34 +23638,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H357" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I357" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H357" s="5" t="n">
+        <v>6515000</v>
+      </c>
+      <c r="I357" s="5" t="n">
+        <v>25956</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L357" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K357" s="5" t="n">
+        <v>5733200</v>
+      </c>
+      <c r="L357" s="5" t="n">
+        <v>22841</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N357" s="3" t="inlineStr">
@@ -24524,7 +24212,7 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -24532,34 +24220,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H366" s="5" t="n">
+        <v>6495000</v>
+      </c>
+      <c r="I366" s="5" t="n">
+        <v>25876</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L366" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K366" s="5" t="n">
+        <v>5715600</v>
+      </c>
+      <c r="L366" s="5" t="n">
+        <v>22771</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -25114,7 +24794,7 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -25122,34 +24802,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H375" s="5" t="n">
+        <v>6476000</v>
+      </c>
+      <c r="I375" s="5" t="n">
+        <v>25801</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L375" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K375" s="5" t="n">
+        <v>5698880</v>
+      </c>
+      <c r="L375" s="5" t="n">
+        <v>22705</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N375" s="3" t="inlineStr">
@@ -25704,7 +25376,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -25712,34 +25384,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H384" s="5" t="n">
+        <v>6457000</v>
+      </c>
+      <c r="I384" s="5" t="n">
+        <v>25725</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K384" s="5" t="n">
+        <v>5682160</v>
+      </c>
+      <c r="L384" s="5" t="n">
+        <v>22638</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -26294,7 +25958,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -26302,34 +25966,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H393" s="5" t="n">
+        <v>6437000</v>
+      </c>
+      <c r="I393" s="5" t="n">
+        <v>25645</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L393" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K393" s="5" t="n">
+        <v>5664560</v>
+      </c>
+      <c r="L393" s="5" t="n">
+        <v>22568</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N393" s="3" t="inlineStr">
@@ -27210,7 +26866,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -27218,34 +26874,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H407" s="5" t="n">
+        <v>8724000</v>
+      </c>
+      <c r="I407" s="5" t="n">
+        <v>27521</v>
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L407" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K407" s="5" t="n">
+        <v>7677120</v>
+      </c>
+      <c r="L407" s="5" t="n">
+        <v>24218</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N407" s="3" t="inlineStr">
@@ -27482,7 +27130,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -27490,34 +27138,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H411" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I411" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H411" s="5" t="n">
+        <v>9673000</v>
+      </c>
+      <c r="I411" s="5" t="n">
+        <v>29401</v>
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K411" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L411" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K411" s="5" t="n">
+        <v>8512240</v>
+      </c>
+      <c r="L411" s="5" t="n">
+        <v>25873</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N411" s="3" t="inlineStr">
@@ -27862,7 +27502,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -27870,34 +27510,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H417" s="5" t="n">
+        <v>8698000</v>
+      </c>
+      <c r="I417" s="5" t="n">
+        <v>27438</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L417" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K417" s="5" t="n">
+        <v>7654240</v>
+      </c>
+      <c r="L417" s="5" t="n">
+        <v>24146</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N417" s="3" t="inlineStr">
@@ -28134,7 +27766,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -28142,34 +27774,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H421" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I421" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H421" s="5" t="n">
+        <v>9644000</v>
+      </c>
+      <c r="I421" s="5" t="n">
+        <v>29313</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K421" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L421" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K421" s="5" t="n">
+        <v>8486720</v>
+      </c>
+      <c r="L421" s="5" t="n">
+        <v>25796</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N421" s="3" t="inlineStr">
@@ -28514,7 +28138,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -28522,34 +28146,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H427" s="5" t="n">
+        <v>8672000</v>
+      </c>
+      <c r="I427" s="5" t="n">
+        <v>27356</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K427" s="5" t="n">
+        <v>7631360</v>
+      </c>
+      <c r="L427" s="5" t="n">
+        <v>24074</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N427" s="3" t="inlineStr">
@@ -28778,7 +28394,7 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -28786,34 +28402,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H431" s="5" t="n">
+        <v>9586000</v>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>29137</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L431" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K431" s="5" t="n">
+        <v>8435680</v>
+      </c>
+      <c r="L431" s="5" t="n">
+        <v>25640</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N431" s="3" t="inlineStr">
@@ -29158,7 +28766,7 @@
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -29166,34 +28774,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H437" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I437" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H437" s="5" t="n">
+        <v>8621000</v>
+      </c>
+      <c r="I437" s="5" t="n">
+        <v>27196</v>
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K437" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L437" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K437" s="5" t="n">
+        <v>7586480</v>
+      </c>
+      <c r="L437" s="5" t="n">
+        <v>23932</v>
       </c>
       <c r="M437" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N437" s="3" t="inlineStr">
@@ -29422,7 +29022,7 @@
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -29430,34 +29030,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H441" s="5" t="n">
+        <v>9557000</v>
+      </c>
+      <c r="I441" s="5" t="n">
+        <v>29049</v>
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L441" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K441" s="5" t="n">
+        <v>8410160</v>
+      </c>
+      <c r="L441" s="5" t="n">
+        <v>25563</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N441" s="3" t="inlineStr">
@@ -29802,7 +29394,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
@@ -29810,34 +29402,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H447" s="5" t="n">
+        <v>8595000</v>
+      </c>
+      <c r="I447" s="5" t="n">
+        <v>27114</v>
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L447" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K447" s="5" t="n">
+        <v>7563600</v>
+      </c>
+      <c r="L447" s="5" t="n">
+        <v>23860</v>
       </c>
       <c r="M447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N447" s="3" t="inlineStr">
@@ -30066,7 +29650,7 @@
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr">
@@ -30074,34 +29658,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H451" s="5" t="n">
+        <v>9529000</v>
+      </c>
+      <c r="I451" s="5" t="n">
+        <v>28964</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L451" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K451" s="5" t="n">
+        <v>8385520</v>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>25488</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N451" s="3" t="inlineStr">
@@ -30446,7 +30022,7 @@
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G457" s="3" t="inlineStr">
@@ -30454,34 +30030,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H457" s="5" t="n">
+        <v>8569000</v>
+      </c>
+      <c r="I457" s="5" t="n">
+        <v>27032</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L457" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K457" s="5" t="n">
+        <v>7540720</v>
+      </c>
+      <c r="L457" s="5" t="n">
+        <v>23788</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N457" s="3" t="inlineStr">
@@ -30702,7 +30270,7 @@
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -30710,34 +30278,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H461" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I461" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H461" s="5" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="I461" s="5" t="n">
+        <v>28875</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K461" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L461" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K461" s="5" t="n">
+        <v>8360000</v>
+      </c>
+      <c r="L461" s="5" t="n">
+        <v>25410</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N461" s="3" t="inlineStr">
@@ -31082,7 +30642,7 @@
       </c>
       <c r="F467" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G467" s="3" t="inlineStr">
@@ -31090,34 +30650,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H467" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I467" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H467" s="5" t="n">
+        <v>8543000</v>
+      </c>
+      <c r="I467" s="5" t="n">
+        <v>26950</v>
       </c>
       <c r="J467" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K467" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L467" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K467" s="5" t="n">
+        <v>7517840</v>
+      </c>
+      <c r="L467" s="5" t="n">
+        <v>23716</v>
       </c>
       <c r="M467" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N467" s="3" t="inlineStr">
@@ -31276,7 +30828,7 @@
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -31284,31 +30836,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H470" s="5" t="n">
-        <v>17510000</v>
-      </c>
-      <c r="I470" s="5" t="n">
-        <v>28242</v>
+      <c r="H470" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I470" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K470" s="5" t="n">
-        <v>15408800</v>
-      </c>
-      <c r="L470" s="5" t="n">
-        <v>24853</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L470" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N470" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31338,7 +30898,7 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
@@ -31346,34 +30906,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H471" s="5" t="n">
+        <v>9472000</v>
+      </c>
+      <c r="I471" s="5" t="n">
+        <v>28790</v>
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L471" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K471" s="5" t="n">
+        <v>8335360</v>
+      </c>
+      <c r="L471" s="5" t="n">
+        <v>25335</v>
       </c>
       <c r="M471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N471" s="3" t="inlineStr">
@@ -31718,7 +31270,7 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -31726,34 +31278,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H477" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I477" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H477" s="5" t="n">
+        <v>8518000</v>
+      </c>
+      <c r="I477" s="5" t="n">
+        <v>26871</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K477" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L477" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K477" s="5" t="n">
+        <v>7495840</v>
+      </c>
+      <c r="L477" s="5" t="n">
+        <v>23646</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N477" s="3" t="inlineStr">
@@ -32346,7 +31890,7 @@
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr">
@@ -32354,34 +31898,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H487" s="5" t="n">
+        <v>8492000</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>26789</v>
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L487" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K487" s="5" t="n">
+        <v>7472960</v>
+      </c>
+      <c r="L487" s="5" t="n">
+        <v>23574</v>
       </c>
       <c r="M487" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N487" s="3" t="inlineStr">
@@ -32974,7 +32510,7 @@
       </c>
       <c r="F497" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G497" s="3" t="inlineStr">
@@ -32982,34 +32518,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H497" s="5" t="n">
+        <v>8467000</v>
+      </c>
+      <c r="I497" s="5" t="n">
+        <v>26710</v>
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L497" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K497" s="5" t="n">
+        <v>7450960</v>
+      </c>
+      <c r="L497" s="5" t="n">
+        <v>23505</v>
       </c>
       <c r="M497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N497" s="3" t="inlineStr">
@@ -33602,7 +33130,7 @@
       </c>
       <c r="F507" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G507" s="3" t="inlineStr">
@@ -33610,34 +33138,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H507" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I507" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H507" s="5" t="n">
+        <v>8442000</v>
+      </c>
+      <c r="I507" s="5" t="n">
+        <v>26631</v>
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K507" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L507" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K507" s="5" t="n">
+        <v>7428960</v>
+      </c>
+      <c r="L507" s="5" t="n">
+        <v>23435</v>
       </c>
       <c r="M507" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N507" s="3" t="inlineStr">
@@ -33796,7 +33316,7 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -33804,31 +33324,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H510" s="5" t="n">
-        <v>17302000</v>
-      </c>
-      <c r="I510" s="5" t="n">
-        <v>27906</v>
+      <c r="H510" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I510" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K510" s="5" t="n">
-        <v>15225760</v>
-      </c>
-      <c r="L510" s="5" t="n">
-        <v>24558</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K510" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L510" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M510" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N510" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34230,7 +33758,7 @@
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G517" s="3" t="inlineStr">
@@ -34238,34 +33766,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H517" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I517" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H517" s="5" t="n">
+        <v>8416000</v>
+      </c>
+      <c r="I517" s="5" t="n">
+        <v>26549</v>
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K517" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L517" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K517" s="5" t="n">
+        <v>7406080</v>
+      </c>
+      <c r="L517" s="5" t="n">
+        <v>23363</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N517" s="3" t="inlineStr">
@@ -34858,7 +34378,7 @@
       </c>
       <c r="F527" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G527" s="3" t="inlineStr">
@@ -34866,34 +34386,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H527" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I527" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H527" s="5" t="n">
+        <v>8366000</v>
+      </c>
+      <c r="I527" s="5" t="n">
+        <v>26391</v>
       </c>
       <c r="J527" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K527" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L527" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K527" s="5" t="n">
+        <v>7362080</v>
+      </c>
+      <c r="L527" s="5" t="n">
+        <v>23224</v>
       </c>
       <c r="M527" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N527" s="3" t="inlineStr">
@@ -35052,7 +34564,7 @@
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr">
@@ -35060,31 +34572,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H530" s="5" t="n">
-        <v>17147000</v>
-      </c>
-      <c r="I530" s="5" t="n">
-        <v>27656</v>
+      <c r="H530" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I530" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J530" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K530" s="5" t="n">
-        <v>15089360</v>
-      </c>
-      <c r="L530" s="5" t="n">
-        <v>24338</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K530" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L530" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M530" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35486,7 +35006,7 @@
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
@@ -35494,34 +35014,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H537" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I537" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H537" s="5" t="n">
+        <v>8341000</v>
+      </c>
+      <c r="I537" s="5" t="n">
+        <v>26312</v>
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K537" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L537" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K537" s="5" t="n">
+        <v>7340080</v>
+      </c>
+      <c r="L537" s="5" t="n">
+        <v>23155</v>
       </c>
       <c r="M537" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N537" s="3" t="inlineStr">
@@ -36114,7 +35626,7 @@
       </c>
       <c r="F547" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G547" s="3" t="inlineStr">
@@ -36122,34 +35634,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H547" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I547" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H547" s="5" t="n">
+        <v>8316000</v>
+      </c>
+      <c r="I547" s="5" t="n">
+        <v>26233</v>
       </c>
       <c r="J547" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K547" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L547" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K547" s="5" t="n">
+        <v>7318080</v>
+      </c>
+      <c r="L547" s="5" t="n">
+        <v>23085</v>
       </c>
       <c r="M547" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N547" s="3" t="inlineStr">
@@ -36316,31 +35820,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H550" s="5" t="n">
-        <v>17044000</v>
-      </c>
-      <c r="I550" s="5" t="n">
-        <v>27490</v>
+      <c r="H550" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I550" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K550" s="5" t="n">
-        <v>14998720</v>
-      </c>
-      <c r="L550" s="5" t="n">
-        <v>24191</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K550" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L550" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N550" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36742,7 +36254,7 @@
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
@@ -36750,34 +36262,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H557" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I557" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H557" s="5" t="n">
+        <v>8291000</v>
+      </c>
+      <c r="I557" s="5" t="n">
+        <v>26155</v>
       </c>
       <c r="J557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K557" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L557" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K557" s="5" t="n">
+        <v>7296080</v>
+      </c>
+      <c r="L557" s="5" t="n">
+        <v>23016</v>
       </c>
       <c r="M557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N557" s="3" t="inlineStr">
@@ -37370,7 +36874,7 @@
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
@@ -37378,34 +36882,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H567" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I567" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H567" s="5" t="n">
+        <v>8267000</v>
+      </c>
+      <c r="I567" s="5" t="n">
+        <v>26079</v>
       </c>
       <c r="J567" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K567" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L567" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K567" s="5" t="n">
+        <v>7274960</v>
+      </c>
+      <c r="L567" s="5" t="n">
+        <v>22949</v>
       </c>
       <c r="M567" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N567" s="3" t="inlineStr">
@@ -37998,7 +37494,7 @@
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G577" s="3" t="inlineStr">
@@ -38006,34 +37502,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H577" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I577" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H577" s="5" t="n">
+        <v>8242000</v>
+      </c>
+      <c r="I577" s="5" t="n">
+        <v>26000</v>
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K577" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L577" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K577" s="5" t="n">
+        <v>7252960</v>
+      </c>
+      <c r="L577" s="5" t="n">
+        <v>22880</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N577" s="3" t="inlineStr">
@@ -38626,7 +38114,7 @@
       </c>
       <c r="F587" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
@@ -38634,34 +38122,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H587" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I587" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H587" s="5" t="n">
+        <v>8217000</v>
+      </c>
+      <c r="I587" s="5" t="n">
+        <v>25921</v>
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K587" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L587" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K587" s="5" t="n">
+        <v>7230960</v>
+      </c>
+      <c r="L587" s="5" t="n">
+        <v>22811</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N587" s="3" t="inlineStr">
@@ -39254,7 +38734,7 @@
       </c>
       <c r="F597" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G597" s="3" t="inlineStr">
@@ -39262,34 +38742,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H597" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I597" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H597" s="5" t="n">
+        <v>8193000</v>
+      </c>
+      <c r="I597" s="5" t="n">
+        <v>25845</v>
       </c>
       <c r="J597" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K597" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L597" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K597" s="5" t="n">
+        <v>7209840</v>
+      </c>
+      <c r="L597" s="5" t="n">
+        <v>22744</v>
       </c>
       <c r="M597" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N597" s="3" t="inlineStr">
@@ -39882,7 +39354,7 @@
       </c>
       <c r="F607" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G607" s="3" t="inlineStr">
@@ -39890,34 +39362,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H607" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I607" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H607" s="5" t="n">
+        <v>8144000</v>
+      </c>
+      <c r="I607" s="5" t="n">
+        <v>25691</v>
       </c>
       <c r="J607" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K607" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L607" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K607" s="5" t="n">
+        <v>7166720</v>
+      </c>
+      <c r="L607" s="5" t="n">
+        <v>22608</v>
       </c>
       <c r="M607" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N607" s="3" t="inlineStr">
@@ -40138,7 +39602,7 @@
       </c>
       <c r="F611" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G611" s="3" t="inlineStr">
@@ -40146,34 +39610,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H611" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I611" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H611" s="5" t="n">
+        <v>9029000</v>
+      </c>
+      <c r="I611" s="5" t="n">
+        <v>27444</v>
       </c>
       <c r="J611" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K611" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L611" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K611" s="5" t="n">
+        <v>7945520</v>
+      </c>
+      <c r="L611" s="5" t="n">
+        <v>24151</v>
       </c>
       <c r="M611" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N611" s="3" t="inlineStr">
@@ -40518,7 +39974,7 @@
       </c>
       <c r="F617" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G617" s="3" t="inlineStr">
@@ -40526,34 +39982,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H617" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I617" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H617" s="5" t="n">
+        <v>8119000</v>
+      </c>
+      <c r="I617" s="5" t="n">
+        <v>25612</v>
       </c>
       <c r="J617" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K617" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L617" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K617" s="5" t="n">
+        <v>7144720</v>
+      </c>
+      <c r="L617" s="5" t="n">
+        <v>22539</v>
       </c>
       <c r="M617" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N617" s="3" t="inlineStr">
@@ -40774,7 +40222,7 @@
       </c>
       <c r="F621" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G621" s="3" t="inlineStr">
@@ -40782,34 +40230,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H621" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I621" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H621" s="5" t="n">
+        <v>9002000</v>
+      </c>
+      <c r="I621" s="5" t="n">
+        <v>27362</v>
       </c>
       <c r="J621" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K621" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L621" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K621" s="5" t="n">
+        <v>7921760</v>
+      </c>
+      <c r="L621" s="5" t="n">
+        <v>24078</v>
       </c>
       <c r="M621" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N621" s="3" t="inlineStr">
@@ -41154,7 +40594,7 @@
       </c>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G627" s="3" t="inlineStr">
@@ -41162,34 +40602,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H627" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I627" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H627" s="5" t="n">
+        <v>8095000</v>
+      </c>
+      <c r="I627" s="5" t="n">
+        <v>25536</v>
       </c>
       <c r="J627" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K627" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L627" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K627" s="5" t="n">
+        <v>7123600</v>
+      </c>
+      <c r="L627" s="5" t="n">
+        <v>22472</v>
       </c>
       <c r="M627" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N627" s="3" t="inlineStr">
@@ -41410,7 +40842,7 @@
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G631" s="3" t="inlineStr">
@@ -41418,34 +40850,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H631" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I631" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H631" s="5" t="n">
+        <v>8975000</v>
+      </c>
+      <c r="I631" s="5" t="n">
+        <v>27280</v>
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K631" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L631" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K631" s="5" t="n">
+        <v>7898000</v>
+      </c>
+      <c r="L631" s="5" t="n">
+        <v>24006</v>
       </c>
       <c r="M631" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N631" s="3" t="inlineStr">
@@ -41790,7 +41214,7 @@
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G637" s="3" t="inlineStr">
@@ -41798,34 +41222,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H637" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I637" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H637" s="5" t="n">
+        <v>8015000</v>
+      </c>
+      <c r="I637" s="5" t="n">
+        <v>25284</v>
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K637" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L637" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K637" s="5" t="n">
+        <v>7053200</v>
+      </c>
+      <c r="L637" s="5" t="n">
+        <v>22250</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N637" s="3" t="inlineStr">
@@ -42046,7 +41462,7 @@
       </c>
       <c r="F641" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G641" s="3" t="inlineStr">
@@ -42054,34 +41470,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H641" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I641" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H641" s="5" t="n">
+        <v>8948000</v>
+      </c>
+      <c r="I641" s="5" t="n">
+        <v>27198</v>
       </c>
       <c r="J641" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K641" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L641" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K641" s="5" t="n">
+        <v>7874240</v>
+      </c>
+      <c r="L641" s="5" t="n">
+        <v>23934</v>
       </c>
       <c r="M641" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N641" s="3" t="inlineStr">
@@ -42426,7 +41834,7 @@
       </c>
       <c r="F647" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G647" s="3" t="inlineStr">
@@ -42434,34 +41842,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H647" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I647" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H647" s="5" t="n">
+        <v>7782000</v>
+      </c>
+      <c r="I647" s="5" t="n">
+        <v>24549</v>
       </c>
       <c r="J647" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K647" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L647" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K647" s="5" t="n">
+        <v>6848160</v>
+      </c>
+      <c r="L647" s="5" t="n">
+        <v>21603</v>
       </c>
       <c r="M647" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N647" s="3" t="inlineStr">
@@ -42736,22 +42136,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -44325,12 +43725,12 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 280呎 (1房)
--
--
-(待售)</t>
+$761万
+$27,164/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -44440,22 +43840,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -44549,12 +43949,12 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
--
--
-(待售)</t>
+$682万
+$27,280/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -44573,12 +43973,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$719万
+$28,661/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
@@ -44628,20 +44028,20 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="22" t="inlineStr">
+$680万
+$27,196/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$889万
+$27,533/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -44652,12 +44052,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$717万
+$28,574/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -44707,20 +44107,20 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
+$678万
+$27,116/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$887万
+$27,452/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -44731,12 +44131,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$715万
+$28,490/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -44786,20 +44186,20 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
+$674万
+$26,956/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$881万
+$27,288/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -44810,12 +44210,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$711万
+$28,319/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -44865,20 +44265,20 @@
 (26年-07月-01日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
+$672万
+$26,872/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$879万
+$27,207/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -44889,12 +44289,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$709万
+$28,235/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -44952,12 +44352,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$876万
+$27,124/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -44968,12 +44368,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$706万
+$28,147/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -45031,12 +44431,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$874万
+$27,043/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -45047,12 +44447,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$704万
+$28,064/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -45110,12 +44510,12 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$871万
+$26,963/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -45126,12 +44526,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$702万
+$27,980/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -45189,12 +44589,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$868万
+$26,882/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -45205,12 +44605,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$700万
+$27,896/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -45268,12 +44668,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$866万
+$26,802/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -45284,12 +44684,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$698万
+$27,813/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -45347,12 +44747,12 @@
 (24年-07月-01日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$863万
+$26,721/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -45363,12 +44763,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$696万
+$27,729/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -45426,12 +44826,12 @@
 (26年-04月-07日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$860万
+$26,641/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -45442,12 +44842,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$694万
+$27,649/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -45505,12 +44905,12 @@
 (26年-05月-31日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
--
--
-(待售)</t>
+$855万
+$26,483/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -45521,12 +44921,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$690万
+$27,482/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -45600,12 +45000,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$688万
+$27,402/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -45679,12 +45079,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$686万
+$27,319/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -45758,12 +45158,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$684万
+$27,239/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -45837,12 +45237,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$682万
+$27,155/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -45916,12 +45316,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$680万
+$27,076/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -45995,12 +45395,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$678万
+$26,992/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -46074,12 +45474,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$665万
+$26,510/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -46153,12 +45553,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$652万
+$25,956/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -46232,12 +45632,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$650万
+$25,876/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -46311,12 +45711,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$648万
+$25,801/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -46390,12 +45790,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$646万
+$25,725/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -46469,12 +45869,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
--
--
-(待售)</t>
+$644万
+$25,645/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -46569,7 +45969,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -46579,12 +45979,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -46675,12 +46075,12 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$872万
+$27,521/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -46762,12 +46162,12 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$870万
+$27,438/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -46810,12 +46210,12 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$967万
+$29,401/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -46849,12 +46249,12 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$867万
+$27,356/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -46897,12 +46297,12 @@
 (26年-06月-21日)</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$964万
+$29,313/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -46936,12 +46336,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$862万
+$27,196/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -46984,12 +46384,12 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$959万
+$29,137/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -47023,12 +46423,12 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$860万
+$27,114/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -47071,12 +46471,12 @@
 (26年-06月-14日)</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$956万
+$29,049/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -47110,12 +46510,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$857万
+$27,032/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -47158,12 +46558,12 @@
 (26年-05月-03日)</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$953万
+$28,964/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -47173,12 +46573,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1751万
-$28,242/呎
-(暂停销售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -47197,12 +46597,12 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$854万
+$26,950/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -47245,12 +46645,12 @@
 (24年-08月-01日)</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$950万
+$28,875/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -47284,12 +46684,12 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$852万
+$26,871/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -47332,12 +46732,12 @@
 (24年-11月-12日)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$947万
+$28,790/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -47371,12 +46771,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$849万
+$26,789/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -47458,12 +46858,12 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$847万
+$26,710/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -47521,12 +46921,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1730万
-$27,906/呎
-(暂停销售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -47545,12 +46945,12 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$844万
+$26,631/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -47632,12 +47032,12 @@
 (26年-05月-03日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$842万
+$26,549/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -47695,12 +47095,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1715万
-$27,656/呎
-(暂停销售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -47719,12 +47119,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$837万
+$26,391/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -47806,12 +47206,12 @@
 (26年-04月-26日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$834万
+$26,312/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -47872,8 +47272,8 @@
       <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-$1704万
-$27,490/呎
+招标单位
+-
 (已定价未售)</t>
         </is>
       </c>
@@ -47893,12 +47293,12 @@
 (26年-02月-24日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$832万
+$26,233/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -47980,12 +47380,12 @@
 (26年-04月-19日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$829万
+$26,155/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -48067,12 +47467,12 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$827万
+$26,079/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -48154,12 +47554,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$824万
+$26,000/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -48241,12 +47641,12 @@
 (26年-05月-10日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$822万
+$25,921/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -48328,12 +47728,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$819万
+$25,845/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -48415,12 +47815,12 @@
 (26年-05月-03日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$814万
+$25,691/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -48502,12 +47902,12 @@
 (26年-04月-29日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$812万
+$25,612/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -48550,12 +47950,12 @@
 (24年-05月-29日)</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K26" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$903万
+$27,444/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -48589,12 +47989,12 @@
 (26年-05月-17日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$810万
+$25,536/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -48637,12 +48037,12 @@
 (24年-05月-26日)</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K27" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$900万
+$27,362/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -48676,12 +48076,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$802万
+$25,284/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -48724,12 +48124,12 @@
 (24年-06月-04日)</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K28" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$898万
+$27,280/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -48763,12 +48163,12 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
--
--
-(待售)</t>
+$778万
+$24,549/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -48811,12 +48211,12 @@
 (24年-11月-04日)</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="K29" s="24" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
--
--
-(待售)</t>
+$895万
+$27,198/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
